--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6496EE2-B504-4281-96DE-2C52B8DB003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6909427-7650-467B-B326-121C8B19943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="13" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,18 @@
     <sheet name="11-3" sheetId="9" r:id="rId9"/>
     <sheet name="12-3" sheetId="10" r:id="rId10"/>
     <sheet name="13-3" sheetId="11" r:id="rId11"/>
+    <sheet name="14-3" sheetId="12" r:id="rId12"/>
+    <sheet name="16-3" sheetId="13" r:id="rId13"/>
+    <sheet name="17-3" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'10-3'!$A$2:$Q$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'11-3'!$A$2:$Q$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'12-3'!$A$2:$Q$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'13-3'!$A$2:$Q$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'14-3'!$A$2:$Q$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-3'!$A$2:$Q$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'17-3'!$A$2:$P$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2-3'!$A$2:$Q$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4-3'!$A$2:$Q$47</definedName>
@@ -57,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4679" uniqueCount="1567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="1894">
   <si>
     <t>THU 2</t>
   </si>
@@ -4758,6 +4764,987 @@
   </si>
   <si>
     <t>T6.13.3.2026</t>
+  </si>
+  <si>
+    <t>NGAY 14-3</t>
+  </si>
+  <si>
+    <t>hd001607</t>
+  </si>
+  <si>
+    <t>le thanh ton</t>
+  </si>
+  <si>
+    <t>14-03-2026.</t>
+  </si>
+  <si>
+    <t>hsu</t>
+  </si>
+  <si>
+    <t>hd001608</t>
+  </si>
+  <si>
+    <t>2A/14,</t>
+  </si>
+  <si>
+    <t>hang pu</t>
+  </si>
+  <si>
+    <t>hd001523</t>
+  </si>
+  <si>
+    <t>74/2,</t>
+  </si>
+  <si>
+    <t>ngoc pham</t>
+  </si>
+  <si>
+    <t>hd001576</t>
+  </si>
+  <si>
+    <t>ba huyen thanh quan</t>
+  </si>
+  <si>
+    <t>sam</t>
+  </si>
+  <si>
+    <t>hd001502</t>
+  </si>
+  <si>
+    <t>miu phung</t>
+  </si>
+  <si>
+    <t>hd001634</t>
+  </si>
+  <si>
+    <t>kh ck 875</t>
+  </si>
+  <si>
+    <t>lyka</t>
+  </si>
+  <si>
+    <t>huyen nguyen</t>
+  </si>
+  <si>
+    <t>hd001636</t>
+  </si>
+  <si>
+    <t>623/43,</t>
+  </si>
+  <si>
+    <t>dinh luong</t>
+  </si>
+  <si>
+    <t>hd001559</t>
+  </si>
+  <si>
+    <t>nguyen duy duong</t>
+  </si>
+  <si>
+    <t>hd000475</t>
+  </si>
+  <si>
+    <t>nguyen thuong hien</t>
+  </si>
+  <si>
+    <t>ly ly nguyen</t>
+  </si>
+  <si>
+    <t>hd001619</t>
+  </si>
+  <si>
+    <t>CC A3</t>
+  </si>
+  <si>
+    <t>hd001620</t>
+  </si>
+  <si>
+    <t>nhung xuxy</t>
+  </si>
+  <si>
+    <t>hd001631</t>
+  </si>
+  <si>
+    <t>2/11,</t>
+  </si>
+  <si>
+    <t>thien phuoc</t>
+  </si>
+  <si>
+    <t>tuyet nhung</t>
+  </si>
+  <si>
+    <t>hd001552</t>
+  </si>
+  <si>
+    <t>AT 14-3</t>
+  </si>
+  <si>
+    <t>my nhung</t>
+  </si>
+  <si>
+    <t>hd001593</t>
+  </si>
+  <si>
+    <t>ds9</t>
+  </si>
+  <si>
+    <t>tran thu thaoo</t>
+  </si>
+  <si>
+    <t>hd001499</t>
+  </si>
+  <si>
+    <t>toa A1</t>
+  </si>
+  <si>
+    <t>pham nhu y</t>
+  </si>
+  <si>
+    <t>hd001455</t>
+  </si>
+  <si>
+    <t>duong F</t>
+  </si>
+  <si>
+    <t>hd001618</t>
+  </si>
+  <si>
+    <t>nguyen thi kim thoa</t>
+  </si>
+  <si>
+    <t>hd001465</t>
+  </si>
+  <si>
+    <t>25a</t>
+  </si>
+  <si>
+    <t>be loan</t>
+  </si>
+  <si>
+    <t>hd001561</t>
+  </si>
+  <si>
+    <t>631/49,</t>
+  </si>
+  <si>
+    <t>tl10</t>
+  </si>
+  <si>
+    <t>bao thi</t>
+  </si>
+  <si>
+    <t>hd001492</t>
+  </si>
+  <si>
+    <t>47/15,</t>
+  </si>
+  <si>
+    <t>bui thi lung</t>
+  </si>
+  <si>
+    <t>diem my</t>
+  </si>
+  <si>
+    <t>hd001590</t>
+  </si>
+  <si>
+    <t>ds29</t>
+  </si>
+  <si>
+    <t>hd001458</t>
+  </si>
+  <si>
+    <t>phan thanh my</t>
+  </si>
+  <si>
+    <t>hd001638</t>
+  </si>
+  <si>
+    <t>730/7/2A</t>
+  </si>
+  <si>
+    <t>hd001591</t>
+  </si>
+  <si>
+    <t>pham thi bao tram</t>
+  </si>
+  <si>
+    <t>hd001398</t>
+  </si>
+  <si>
+    <t>13/28,</t>
+  </si>
+  <si>
+    <t>ds35</t>
+  </si>
+  <si>
+    <t>trang pham</t>
+  </si>
+  <si>
+    <t>hd001633</t>
+  </si>
+  <si>
+    <t>16/3,</t>
+  </si>
+  <si>
+    <t>T7.14.3.2026</t>
+  </si>
+  <si>
+    <t>đơn trả 16-3</t>
+  </si>
+  <si>
+    <t>NGAY 16-3</t>
+  </si>
+  <si>
+    <t>tho bunny</t>
+  </si>
+  <si>
+    <t>hd002074</t>
+  </si>
+  <si>
+    <t>auqa 2</t>
+  </si>
+  <si>
+    <t>16-03-2026.</t>
+  </si>
+  <si>
+    <t>hd002319</t>
+  </si>
+  <si>
+    <t>lucy nguyen</t>
+  </si>
+  <si>
+    <t>hd001678</t>
+  </si>
+  <si>
+    <t>cc soho</t>
+  </si>
+  <si>
+    <t>co giang</t>
+  </si>
+  <si>
+    <t>linh thu</t>
+  </si>
+  <si>
+    <t>hd002295</t>
+  </si>
+  <si>
+    <t>87A</t>
+  </si>
+  <si>
+    <t>ham nghi</t>
+  </si>
+  <si>
+    <t>hd002333</t>
+  </si>
+  <si>
+    <t>36/23,</t>
+  </si>
+  <si>
+    <t>bo thi kieu ni</t>
+  </si>
+  <si>
+    <t>hd001876</t>
+  </si>
+  <si>
+    <t>thuy nguyen</t>
+  </si>
+  <si>
+    <t>hd002326</t>
+  </si>
+  <si>
+    <t>2A/4,</t>
+  </si>
+  <si>
+    <t>bao tram le</t>
+  </si>
+  <si>
+    <t>hd002029</t>
+  </si>
+  <si>
+    <t>ngoc bin</t>
+  </si>
+  <si>
+    <t>hd002086</t>
+  </si>
+  <si>
+    <t>lux 6</t>
+  </si>
+  <si>
+    <t>hd001744</t>
+  </si>
+  <si>
+    <t>61/14,</t>
+  </si>
+  <si>
+    <t>hd002325</t>
+  </si>
+  <si>
+    <t>thanh thao</t>
+  </si>
+  <si>
+    <t>hd001858</t>
+  </si>
+  <si>
+    <t>cc nguyen kim</t>
+  </si>
+  <si>
+    <t>tom ag</t>
+  </si>
+  <si>
+    <t>ho van huep</t>
+  </si>
+  <si>
+    <t>hong ha</t>
+  </si>
+  <si>
+    <t>thao uyen</t>
+  </si>
+  <si>
+    <t>hd001886</t>
+  </si>
+  <si>
+    <t>1/18,</t>
+  </si>
+  <si>
+    <t>nguyen van vinh</t>
+  </si>
+  <si>
+    <t>huynh tam</t>
+  </si>
+  <si>
+    <t>hd002036</t>
+  </si>
+  <si>
+    <t>hd001917</t>
+  </si>
+  <si>
+    <t>AT 16-3</t>
+  </si>
+  <si>
+    <t>amy barbie</t>
+  </si>
+  <si>
+    <t>hd001856</t>
+  </si>
+  <si>
+    <t>nhu y nguyen</t>
+  </si>
+  <si>
+    <t>hd001672</t>
+  </si>
+  <si>
+    <t>hoang thanh hien</t>
+  </si>
+  <si>
+    <t>hd002105</t>
+  </si>
+  <si>
+    <t>hd001563</t>
+  </si>
+  <si>
+    <t>nhien nhien</t>
+  </si>
+  <si>
+    <t>hd002069</t>
+  </si>
+  <si>
+    <t>11D1</t>
+  </si>
+  <si>
+    <t>sky garden 3</t>
+  </si>
+  <si>
+    <t>linh ho</t>
+  </si>
+  <si>
+    <t>hd001747</t>
+  </si>
+  <si>
+    <t>cc duc khai</t>
+  </si>
+  <si>
+    <t>my loc</t>
+  </si>
+  <si>
+    <t>hd001867</t>
+  </si>
+  <si>
+    <t>destiny my</t>
+  </si>
+  <si>
+    <t>hd002046</t>
+  </si>
+  <si>
+    <t>136/5,</t>
+  </si>
+  <si>
+    <t>nguyen thi tan</t>
+  </si>
+  <si>
+    <t>bui vi thuogn</t>
+  </si>
+  <si>
+    <t>hd002323</t>
+  </si>
+  <si>
+    <t>duong hoai thuong</t>
+  </si>
+  <si>
+    <t>hd001859</t>
+  </si>
+  <si>
+    <t>56/7/15,</t>
+  </si>
+  <si>
+    <t>huynh thi hai</t>
+  </si>
+  <si>
+    <t>minh zu</t>
+  </si>
+  <si>
+    <t>nguyen van qua</t>
+  </si>
+  <si>
+    <t>mei vivi</t>
+  </si>
+  <si>
+    <t>hd001879</t>
+  </si>
+  <si>
+    <t>tan thoi nhat 1b</t>
+  </si>
+  <si>
+    <t>thuong</t>
+  </si>
+  <si>
+    <t>my na</t>
+  </si>
+  <si>
+    <t>hd002103</t>
+  </si>
+  <si>
+    <t>ds9a</t>
+  </si>
+  <si>
+    <t>kieu tin</t>
+  </si>
+  <si>
+    <t>hd001864</t>
+  </si>
+  <si>
+    <t>lily kuan tan</t>
+  </si>
+  <si>
+    <t>hd002241</t>
+  </si>
+  <si>
+    <t>ha cong</t>
+  </si>
+  <si>
+    <t>hd001949</t>
+  </si>
+  <si>
+    <t>hd002163</t>
+  </si>
+  <si>
+    <t>hd002054</t>
+  </si>
+  <si>
+    <t>sha sha</t>
+  </si>
+  <si>
+    <t>hd002320</t>
+  </si>
+  <si>
+    <t>hd001809</t>
+  </si>
+  <si>
+    <t>ngoc tuyet</t>
+  </si>
+  <si>
+    <t>hd001797</t>
+  </si>
+  <si>
+    <t>tran le tram anh</t>
+  </si>
+  <si>
+    <t>hd002034</t>
+  </si>
+  <si>
+    <t>179/13A</t>
+  </si>
+  <si>
+    <t>mia mia</t>
+  </si>
+  <si>
+    <t>hd002217</t>
+  </si>
+  <si>
+    <t>tan huong</t>
+  </si>
+  <si>
+    <t>thai- uyen phuong</t>
+  </si>
+  <si>
+    <t>hd001640</t>
+  </si>
+  <si>
+    <t>thoai ngoc hau</t>
+  </si>
+  <si>
+    <t>doan trang</t>
+  </si>
+  <si>
+    <t>hd001818</t>
+  </si>
+  <si>
+    <t>cc citisoho</t>
+  </si>
+  <si>
+    <t>cat lai</t>
+  </si>
+  <si>
+    <t>han tieu phung</t>
+  </si>
+  <si>
+    <t>hd002164</t>
+  </si>
+  <si>
+    <t>thuy te</t>
+  </si>
+  <si>
+    <t>hd002155</t>
+  </si>
+  <si>
+    <t>ds60tml</t>
+  </si>
+  <si>
+    <t>my dung</t>
+  </si>
+  <si>
+    <t>hd001819</t>
+  </si>
+  <si>
+    <t>ds68</t>
+  </si>
+  <si>
+    <t>hong huong</t>
+  </si>
+  <si>
+    <t>hd002257</t>
+  </si>
+  <si>
+    <t>hd001927</t>
+  </si>
+  <si>
+    <t>hd001732</t>
+  </si>
+  <si>
+    <t>be pham</t>
+  </si>
+  <si>
+    <t>hd002107</t>
+  </si>
+  <si>
+    <t>200E</t>
+  </si>
+  <si>
+    <t>hd002283</t>
+  </si>
+  <si>
+    <t>binh loi</t>
+  </si>
+  <si>
+    <t>ngoc uyen</t>
+  </si>
+  <si>
+    <t>hd002122</t>
+  </si>
+  <si>
+    <t>602/42,</t>
+  </si>
+  <si>
+    <t>andy shk</t>
+  </si>
+  <si>
+    <t>hd002070</t>
+  </si>
+  <si>
+    <t>giang</t>
+  </si>
+  <si>
+    <t>hd002068</t>
+  </si>
+  <si>
+    <t>204/5b</t>
+  </si>
+  <si>
+    <t>nguyen huynh cam tu</t>
+  </si>
+  <si>
+    <t>hd002328</t>
+  </si>
+  <si>
+    <t>paark 1</t>
+  </si>
+  <si>
+    <t>tuyet nhu</t>
+  </si>
+  <si>
+    <t>hd002336</t>
+  </si>
+  <si>
+    <t>park 6a</t>
+  </si>
+  <si>
+    <t>an na</t>
+  </si>
+  <si>
+    <t>hd001742</t>
+  </si>
+  <si>
+    <t>643/24/1g</t>
+  </si>
+  <si>
+    <t>thu truong</t>
+  </si>
+  <si>
+    <t>q nguyen</t>
+  </si>
+  <si>
+    <t>189/46A</t>
+  </si>
+  <si>
+    <t>thanh nguyen</t>
+  </si>
+  <si>
+    <t>hd001692</t>
+  </si>
+  <si>
+    <t>126/21,</t>
+  </si>
+  <si>
+    <t>ds20</t>
+  </si>
+  <si>
+    <t>phuong vo</t>
+  </si>
+  <si>
+    <t>hd001920</t>
+  </si>
+  <si>
+    <t>535/59/4C</t>
+  </si>
+  <si>
+    <t>hd001832</t>
+  </si>
+  <si>
+    <t>pham ngoc minh minh</t>
+  </si>
+  <si>
+    <t>hd000460</t>
+  </si>
+  <si>
+    <t>118/1/9,</t>
+  </si>
+  <si>
+    <t>hd002099</t>
+  </si>
+  <si>
+    <t>yen uy</t>
+  </si>
+  <si>
+    <t>hd001693</t>
+  </si>
+  <si>
+    <t>111/36A</t>
+  </si>
+  <si>
+    <t>hd136482</t>
+  </si>
+  <si>
+    <t>32/28/4b</t>
+  </si>
+  <si>
+    <t>hoang uyen</t>
+  </si>
+  <si>
+    <t>hd001943</t>
+  </si>
+  <si>
+    <t>chung cu 4</t>
+  </si>
+  <si>
+    <t>nhung nguyen</t>
+  </si>
+  <si>
+    <t>hd001865</t>
+  </si>
+  <si>
+    <t>cc urban</t>
+  </si>
+  <si>
+    <t>tran phuong</t>
+  </si>
+  <si>
+    <t>hd001670</t>
+  </si>
+  <si>
+    <t>hoang lan bao chi</t>
+  </si>
+  <si>
+    <t>hd001934</t>
+  </si>
+  <si>
+    <t>long truong</t>
+  </si>
+  <si>
+    <t>hd001581</t>
+  </si>
+  <si>
+    <t>kieu may pham</t>
+  </si>
+  <si>
+    <t>hd001709</t>
+  </si>
+  <si>
+    <t>bs10</t>
+  </si>
+  <si>
+    <t>duyen thuy nguyen</t>
+  </si>
+  <si>
+    <t>hd002278</t>
+  </si>
+  <si>
+    <t>S303</t>
+  </si>
+  <si>
+    <t>hd001751</t>
+  </si>
+  <si>
+    <t>tran trang</t>
+  </si>
+  <si>
+    <t>hd001748</t>
+  </si>
+  <si>
+    <t>vo chi cong</t>
+  </si>
+  <si>
+    <t>T2.16.3.2026</t>
+  </si>
+  <si>
+    <t>đơn trả 17.3</t>
+  </si>
+  <si>
+    <t>ĐOÀN NGÂN CHÂU</t>
+  </si>
+  <si>
+    <t>Hồng Vân</t>
+  </si>
+  <si>
+    <t>HD002584</t>
+  </si>
+  <si>
+    <t>hàng sỉ</t>
+  </si>
+  <si>
+    <t>NGÂN KIM</t>
+  </si>
+  <si>
+    <t>Giáng Hương</t>
+  </si>
+  <si>
+    <t>HD002461</t>
+  </si>
+  <si>
+    <t>MIE</t>
+  </si>
+  <si>
+    <t>TUYẾT NHI ZL2</t>
+  </si>
+  <si>
+    <t>Sun Na</t>
+  </si>
+  <si>
+    <t>HD002443</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD002420</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Ngát</t>
+  </si>
+  <si>
+    <t>HD002462</t>
+  </si>
+  <si>
+    <t>Trần Thị Kim Phương</t>
+  </si>
+  <si>
+    <t>HD002362</t>
+  </si>
+  <si>
+    <t>Lưu Bích Ngọc</t>
+  </si>
+  <si>
+    <t>HD002566</t>
+  </si>
+  <si>
+    <t>Ngọc Thao Vu</t>
+  </si>
+  <si>
+    <t>HD002439</t>
+  </si>
+  <si>
+    <t>c bong fb thu hường</t>
+  </si>
+  <si>
+    <t>HD002509</t>
+  </si>
+  <si>
+    <t>Ngọc Mơ</t>
+  </si>
+  <si>
+    <t>HD002409</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD002339</t>
+  </si>
+  <si>
+    <t>An An</t>
+  </si>
+  <si>
+    <t>HD002510</t>
+  </si>
+  <si>
+    <t>jenny bouti</t>
+  </si>
+  <si>
+    <t>THU SHIP</t>
+  </si>
+  <si>
+    <t>Vũ Nguyễn (phương tw)</t>
+  </si>
+  <si>
+    <t>Nhiew (FB Proud 'Pround)</t>
+  </si>
+  <si>
+    <t>HD002453</t>
+  </si>
+  <si>
+    <t>Kim Chúc</t>
+  </si>
+  <si>
+    <t>HD002412</t>
+  </si>
+  <si>
+    <t>Dang Ngoc Anh</t>
+  </si>
+  <si>
+    <t>HD002417</t>
+  </si>
+  <si>
+    <t>BN8823</t>
+  </si>
+  <si>
+    <t>ĐỊA CHỈ</t>
+  </si>
+  <si>
+    <t>76 đặng nghiêm phường long thạnh mỹ</t>
+  </si>
+  <si>
+    <t>a.quyen</t>
+  </si>
+  <si>
+    <t>17-03-2026</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes Grand park</t>
+  </si>
+  <si>
+    <t>111 đường số 10 phường 13</t>
+  </si>
+  <si>
+    <t>AT 17-03</t>
+  </si>
+  <si>
+    <t>275/14B1 Đặng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>170F Tân Hoà Đông f14</t>
+  </si>
+  <si>
+    <t>Chung cư cardinal court toà B</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận )</t>
+  </si>
+  <si>
+    <t>440 kinh dương vương, an lạc</t>
+  </si>
+  <si>
+    <t>binh tan</t>
+  </si>
+  <si>
+    <t>1870\1\98\14a tỉnh lộ 10 tân tạo</t>
+  </si>
+  <si>
+    <t>133 nguyễn thị nhỏ p9</t>
+  </si>
+  <si>
+    <t>Riviera Points ( The View- Tháp 6) 02 Nguyễn văn tưởng</t>
+  </si>
+  <si>
+    <t>391 phú thọ hòa</t>
+  </si>
+  <si>
+    <t>107/7 huỳnh an khương p5</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>115 Trần Thị Nghỉ, Hạnh Thông</t>
+  </si>
+  <si>
+    <t>401 Quang trung f10</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>74/3 Trần thái tông, phường 15</t>
+  </si>
+  <si>
+    <t>39 Đường Trần Quốc Hoàn, P. 4</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Hẻm 18B/73 Nguyễn thị minh khai đakao</t>
+  </si>
+  <si>
+    <t>G1 galaxy9</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>T3.17.3.2026</t>
+  </si>
+  <si>
+    <t>NGAY 17-3</t>
   </si>
 </sst>
 </file>
@@ -4829,7 +5816,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4878,6 +5865,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -4906,7 +5899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4950,6 +5943,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11570,13 +12567,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E265E1-DC1C-450A-97BF-A07C95C14756}">
   <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -13628,6 +14618,6960 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:Q41" xr:uid="{D9E265E1-DC1C-450A-97BF-A07C95C14756}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FA4FA0-9234-4A34-A692-42F7E963D2C5}">
+  <dimension ref="A1:S48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E3" s="5">
+        <v>190</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>25</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J32" si="0">H3-I3</f>
+        <v>-25</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+      <c r="S3" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>395</v>
+      </c>
+      <c r="I5" s="5">
+        <v>25</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E6" s="5">
+        <v>80</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>25</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5">
+        <v>405</v>
+      </c>
+      <c r="I7" s="5">
+        <v>25</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E8" s="5">
+        <v>109</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="5">
+        <v>4</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>25</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5">
+        <v>30</v>
+      </c>
+      <c r="I9" s="5">
+        <v>30</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="G10" s="5">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>30</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="20">
+        <v>10</v>
+      </c>
+      <c r="H11" s="20">
+        <v>2250</v>
+      </c>
+      <c r="I11" s="20">
+        <v>30</v>
+      </c>
+      <c r="J11" s="20">
+        <f t="shared" si="0"/>
+        <v>2220</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E12" s="5">
+        <v>246</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5">
+        <v>25</v>
+      </c>
+      <c r="I12" s="5">
+        <v>25</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E13" s="5">
+        <v>312</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H13" s="5">
+        <v>520</v>
+      </c>
+      <c r="I13" s="5">
+        <v>20</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14" s="5">
+        <v>730</v>
+      </c>
+      <c r="I14" s="5">
+        <v>20</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>30</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="5">
+        <v>25</v>
+      </c>
+      <c r="I16" s="5">
+        <v>25</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E17" s="5">
+        <v>66</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="G17" s="5">
+        <v>6</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>25</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E18" s="5">
+        <v>13</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G18" s="5">
+        <v>6</v>
+      </c>
+      <c r="H18" s="5">
+        <v>735</v>
+      </c>
+      <c r="I18" s="5">
+        <v>25</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" s="5">
+        <v>6</v>
+      </c>
+      <c r="H19" s="5">
+        <v>770</v>
+      </c>
+      <c r="I19" s="5">
+        <v>30</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G20" s="5">
+        <v>8</v>
+      </c>
+      <c r="H20" s="5">
+        <v>815</v>
+      </c>
+      <c r="I20" s="5">
+        <v>25</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E21" s="5">
+        <v>49</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G21" s="5">
+        <v>8</v>
+      </c>
+      <c r="H21" s="5">
+        <v>410</v>
+      </c>
+      <c r="I21" s="5">
+        <v>30</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E22" s="5">
+        <v>30</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G22" s="5">
+        <v>8</v>
+      </c>
+      <c r="H22" s="5">
+        <v>835</v>
+      </c>
+      <c r="I22" s="5">
+        <v>25</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1640</v>
+      </c>
+      <c r="I23" s="5">
+        <v>30</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H24" s="5">
+        <v>820</v>
+      </c>
+      <c r="I24" s="5">
+        <v>30</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H25" s="5">
+        <v>825</v>
+      </c>
+      <c r="I25" s="5">
+        <v>35</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E26" s="5">
+        <v>56</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5">
+        <v>1350</v>
+      </c>
+      <c r="I26" s="5">
+        <v>30</v>
+      </c>
+      <c r="J26" s="5">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5">
+        <v>410</v>
+      </c>
+      <c r="I27" s="5">
+        <v>30</v>
+      </c>
+      <c r="J27" s="5">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="5">
+        <v>1575</v>
+      </c>
+      <c r="I28" s="5">
+        <v>25</v>
+      </c>
+      <c r="J28" s="5">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5">
+        <v>685</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="5">
+        <v>650</v>
+      </c>
+      <c r="I29" s="5">
+        <v>30</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" si="0"/>
+        <v>620</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="5">
+        <v>770</v>
+      </c>
+      <c r="I30" s="5">
+        <v>30</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="5">
+        <v>390</v>
+      </c>
+      <c r="I31" s="5">
+        <v>30</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="5">
+        <v>820</v>
+      </c>
+      <c r="I32" s="5">
+        <v>30</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f t="shared" ref="H34:S34" si="1">SUBTOTAL(9,H3:H33)</f>
+        <v>17195</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="1"/>
+        <v>16375</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="1"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <v>-390</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="7" t="s">
+        <v>1641</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I39" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="J39" s="11">
+        <f>SUM(J33:J37)</f>
+        <v>15985</v>
+      </c>
+      <c r="K39" s="11">
+        <f>R34</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I40" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="J40" s="13">
+        <f>S33</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="14"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I41" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="J41" s="13">
+        <f>T33</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="14"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I42" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="J42" s="13">
+        <f>U33</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="14"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I43" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="J43" s="13">
+        <f>V33</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I44" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I45" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+    </row>
+    <row r="46" spans="1:19" ht="21" x14ac:dyDescent="0.35">
+      <c r="I46" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="J46" s="19">
+        <f>SUM(J39:J45)</f>
+        <v>15985</v>
+      </c>
+      <c r="K46" s="19">
+        <f>SUM(K39:K43)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D48" s="2">
+        <v>109</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="2">
+        <v>4</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>25</v>
+      </c>
+      <c r="I48" s="2">
+        <f t="shared" ref="I48" si="2">G48-H48</f>
+        <v>-25</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:Q32" xr:uid="{70FA4FA0-9234-4A34-A692-42F7E963D2C5}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>735</v>
+      </c>
+      <c r="I3" s="5">
+        <v>25</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" ref="J3:J64" si="0">H3-I3</f>
+        <v>710</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E4" s="5">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>805</v>
+      </c>
+      <c r="I4" s="5">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>805</v>
+      </c>
+      <c r="I5" s="5">
+        <v>25</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>735</v>
+      </c>
+      <c r="I6" s="5">
+        <v>25</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="G7" s="20">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20">
+        <v>25</v>
+      </c>
+      <c r="I7" s="20">
+        <v>25</v>
+      </c>
+      <c r="J7" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E8" s="5">
+        <v>140</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1495</v>
+      </c>
+      <c r="I8" s="5">
+        <v>25</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="0"/>
+        <v>1470</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>815</v>
+      </c>
+      <c r="I9" s="5">
+        <v>25</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E10" s="5">
+        <v>76</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>745</v>
+      </c>
+      <c r="I10" s="5">
+        <v>25</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>25</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4</v>
+      </c>
+      <c r="H12" s="5">
+        <v>30</v>
+      </c>
+      <c r="I12" s="5">
+        <v>30</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="G13" s="5">
+        <v>5</v>
+      </c>
+      <c r="H13" s="5">
+        <v>815</v>
+      </c>
+      <c r="I13" s="5">
+        <v>25</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E14" s="5">
+        <v>230</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="5">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5">
+        <v>745</v>
+      </c>
+      <c r="I14" s="5">
+        <v>25</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5">
+        <v>745</v>
+      </c>
+      <c r="I15" s="5">
+        <v>25</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5">
+        <v>12</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="5">
+        <v>20</v>
+      </c>
+      <c r="I16" s="5">
+        <v>20</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5">
+        <v>112</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>25</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="5">
+        <v>780</v>
+      </c>
+      <c r="I18" s="5">
+        <v>30</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>25</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="5">
+        <v>735</v>
+      </c>
+      <c r="I20" s="5">
+        <v>25</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>25</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="5">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>30</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5">
+        <v>66</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="G23" s="5">
+        <v>6</v>
+      </c>
+      <c r="H23" s="5">
+        <v>30</v>
+      </c>
+      <c r="I23" s="5">
+        <v>30</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E24" s="5">
+        <v>988</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="G24" s="5">
+        <v>6</v>
+      </c>
+      <c r="H24" s="5">
+        <v>735</v>
+      </c>
+      <c r="I24" s="5">
+        <v>25</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E25" s="5">
+        <v>4</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="G25" s="5">
+        <v>7</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>30</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E26" s="5">
+        <v>5</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G26" s="5">
+        <v>7</v>
+      </c>
+      <c r="H26" s="5">
+        <v>750</v>
+      </c>
+      <c r="I26" s="5">
+        <v>30</v>
+      </c>
+      <c r="J26" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E27" s="20">
+        <v>89</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G27" s="20">
+        <v>7</v>
+      </c>
+      <c r="H27" s="20">
+        <v>0</v>
+      </c>
+      <c r="I27" s="20">
+        <v>30</v>
+      </c>
+      <c r="J27" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G28" s="5">
+        <v>7</v>
+      </c>
+      <c r="H28" s="5">
+        <v>660</v>
+      </c>
+      <c r="I28" s="5">
+        <v>30</v>
+      </c>
+      <c r="J28" s="5">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="G29" s="5">
+        <v>7</v>
+      </c>
+      <c r="H29" s="5">
+        <v>410</v>
+      </c>
+      <c r="I29" s="5">
+        <v>30</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E30" s="5">
+        <v>230</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G30" s="5">
+        <v>8</v>
+      </c>
+      <c r="H30" s="5">
+        <v>745</v>
+      </c>
+      <c r="I30" s="5">
+        <v>25</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G31" s="5">
+        <v>8</v>
+      </c>
+      <c r="H31" s="5">
+        <v>465</v>
+      </c>
+      <c r="I31" s="5">
+        <v>25</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3273</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="G32" s="5">
+        <v>8</v>
+      </c>
+      <c r="H32" s="5">
+        <v>610</v>
+      </c>
+      <c r="I32" s="5">
+        <v>30</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G33" s="5">
+        <v>12</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>30</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5">
+        <v>631</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G34" s="5">
+        <v>12</v>
+      </c>
+      <c r="H34" s="5">
+        <v>655</v>
+      </c>
+      <c r="I34" s="5">
+        <v>35</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" si="0"/>
+        <v>620</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E35" s="5">
+        <v>22</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>1716</v>
+      </c>
+      <c r="G35" s="5">
+        <v>12</v>
+      </c>
+      <c r="H35" s="5">
+        <v>270</v>
+      </c>
+      <c r="I35" s="5">
+        <v>30</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5">
+        <v>61</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G36" s="5">
+        <v>12</v>
+      </c>
+      <c r="H36" s="5">
+        <v>35</v>
+      </c>
+      <c r="I36" s="5">
+        <v>35</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E37" s="5">
+        <v>56</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>35</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E38" s="5">
+        <v>89</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H38" s="5">
+        <v>1560</v>
+      </c>
+      <c r="I38" s="5">
+        <v>30</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="0"/>
+        <v>1530</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E39" s="20">
+        <v>17</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="H39" s="20">
+        <v>2530</v>
+      </c>
+      <c r="I39" s="20">
+        <v>35</v>
+      </c>
+      <c r="J39" s="20">
+        <f t="shared" si="0"/>
+        <v>2495</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N39" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E40" s="20">
+        <v>124</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="H40" s="20">
+        <v>2890</v>
+      </c>
+      <c r="I40" s="20">
+        <v>35</v>
+      </c>
+      <c r="J40" s="20">
+        <f t="shared" si="0"/>
+        <v>2855</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N40" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E41" s="5">
+        <v>104</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H41" s="5">
+        <v>950</v>
+      </c>
+      <c r="I41" s="5">
+        <v>30</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="5">
+        <v>1660</v>
+      </c>
+      <c r="I42" s="5">
+        <v>30</v>
+      </c>
+      <c r="J42" s="5">
+        <f t="shared" si="0"/>
+        <v>1630</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H43" s="5">
+        <v>750</v>
+      </c>
+      <c r="I43" s="5">
+        <v>30</v>
+      </c>
+      <c r="J43" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H44" s="5">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5">
+        <v>45</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="0"/>
+        <v>-45</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44">
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E45" s="5">
+        <v>17</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H45" s="5">
+        <v>375</v>
+      </c>
+      <c r="I45" s="5">
+        <v>25</v>
+      </c>
+      <c r="J45" s="5">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H46" s="5">
+        <v>875</v>
+      </c>
+      <c r="I46" s="5">
+        <v>25</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E47" s="5">
+        <v>350</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H47" s="5">
+        <v>515</v>
+      </c>
+      <c r="I47" s="5">
+        <v>25</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E48" s="5">
+        <v>126</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H48" s="5">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5">
+        <v>25</v>
+      </c>
+      <c r="J48" s="5">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G49" s="5">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5">
+        <v>740</v>
+      </c>
+      <c r="I49" s="5">
+        <v>30</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E50" s="5">
+        <v>145</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G50" s="5">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5">
+        <v>1470</v>
+      </c>
+      <c r="I50" s="5">
+        <v>30</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="0"/>
+        <v>1440</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E51" s="5">
+        <v>35</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G51" s="5">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5">
+        <v>1190</v>
+      </c>
+      <c r="I51" s="5">
+        <v>30</v>
+      </c>
+      <c r="J51" s="5">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E52" s="5">
+        <v>22</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G52" s="5">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5">
+        <v>380</v>
+      </c>
+      <c r="I52" s="5">
+        <v>30</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="5">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5">
+        <v>750</v>
+      </c>
+      <c r="I53" s="5">
+        <v>30</v>
+      </c>
+      <c r="J53" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="5">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5">
+        <v>750</v>
+      </c>
+      <c r="I54" s="5">
+        <v>30</v>
+      </c>
+      <c r="J54" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" s="5">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5">
+        <v>750</v>
+      </c>
+      <c r="I55" s="5">
+        <v>30</v>
+      </c>
+      <c r="J55" s="5">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G56" s="5">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5">
+        <v>870</v>
+      </c>
+      <c r="I56" s="5">
+        <v>30</v>
+      </c>
+      <c r="J56" s="5">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E57" s="5">
+        <v>16</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" s="5">
+        <v>600</v>
+      </c>
+      <c r="I57" s="5">
+        <v>20</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H58" s="5">
+        <v>870</v>
+      </c>
+      <c r="I58" s="5">
+        <v>20</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E59" s="5">
+        <v>208</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H59" s="5">
+        <v>1070</v>
+      </c>
+      <c r="I59" s="5">
+        <v>20</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" s="5">
+        <v>810</v>
+      </c>
+      <c r="I60" s="5">
+        <v>20</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H61" s="5">
+        <v>750</v>
+      </c>
+      <c r="I61" s="5">
+        <v>20</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H62" s="5">
+        <v>850</v>
+      </c>
+      <c r="I62" s="5">
+        <v>20</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H63" s="5">
+        <v>780</v>
+      </c>
+      <c r="I63" s="5">
+        <v>20</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" s="5">
+        <v>4110</v>
+      </c>
+      <c r="I64" s="5">
+        <v>30</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="0"/>
+        <v>4080</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
+      <c r="R64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H65" s="5">
+        <v>30</v>
+      </c>
+      <c r="I65" s="5">
+        <v>30</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" ref="J65:J81" si="1">H65-I65</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5">
+        <v>25</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H67" s="5">
+        <v>1075</v>
+      </c>
+      <c r="I67" s="5">
+        <v>25</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" si="1"/>
+        <v>1050</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H68" s="5">
+        <v>1985</v>
+      </c>
+      <c r="I68" s="5">
+        <v>25</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="1"/>
+        <v>1960</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="R68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>1794</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H69" s="5">
+        <v>385</v>
+      </c>
+      <c r="I69" s="5">
+        <v>25</v>
+      </c>
+      <c r="J69" s="5">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" s="5">
+        <v>815</v>
+      </c>
+      <c r="I70" s="5">
+        <v>25</v>
+      </c>
+      <c r="J70" s="5">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+      <c r="R70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H71" s="5">
+        <v>765</v>
+      </c>
+      <c r="I71" s="5">
+        <v>25</v>
+      </c>
+      <c r="J71" s="5">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="5"/>
+      <c r="R71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H72" s="5">
+        <v>945</v>
+      </c>
+      <c r="I72" s="5">
+        <v>25</v>
+      </c>
+      <c r="J72" s="5">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
+      <c r="R72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H73" s="5">
+        <v>820</v>
+      </c>
+      <c r="I73" s="5">
+        <v>30</v>
+      </c>
+      <c r="J73" s="5">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+      <c r="R73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H74" s="5">
+        <v>970</v>
+      </c>
+      <c r="I74" s="5">
+        <v>30</v>
+      </c>
+      <c r="J74" s="5">
+        <f t="shared" si="1"/>
+        <v>940</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E75" s="5">
+        <v>63</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H75" s="5">
+        <v>1540</v>
+      </c>
+      <c r="I75" s="5">
+        <v>30</v>
+      </c>
+      <c r="J75" s="5">
+        <f t="shared" si="1"/>
+        <v>1510</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M75" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>1811</v>
+      </c>
+      <c r="G76" s="5">
+        <v>9</v>
+      </c>
+      <c r="H76" s="5">
+        <v>380</v>
+      </c>
+      <c r="I76" s="5">
+        <v>30</v>
+      </c>
+      <c r="J76" s="5">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="5"/>
+      <c r="R76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>1811</v>
+      </c>
+      <c r="G77" s="5">
+        <v>9</v>
+      </c>
+      <c r="H77" s="5">
+        <v>790</v>
+      </c>
+      <c r="I77" s="5">
+        <v>30</v>
+      </c>
+      <c r="J77" s="5">
+        <f t="shared" si="1"/>
+        <v>760</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M77" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+      <c r="R77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G78" s="5">
+        <v>9</v>
+      </c>
+      <c r="H78" s="5">
+        <v>740</v>
+      </c>
+      <c r="I78" s="5">
+        <v>30</v>
+      </c>
+      <c r="J78" s="5">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="5"/>
+      <c r="R78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G79" s="5">
+        <v>9</v>
+      </c>
+      <c r="H79" s="5">
+        <v>1740</v>
+      </c>
+      <c r="I79" s="5">
+        <v>30</v>
+      </c>
+      <c r="J79" s="5">
+        <f t="shared" si="1"/>
+        <v>1710</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+      <c r="R79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="G80" s="5">
+        <v>9</v>
+      </c>
+      <c r="H80" s="5">
+        <v>85</v>
+      </c>
+      <c r="I80" s="5">
+        <v>30</v>
+      </c>
+      <c r="J80" s="5">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M80" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="5"/>
+      <c r="R80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E81" s="5">
+        <v>454</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G81" s="5">
+        <v>9</v>
+      </c>
+      <c r="H81" s="5">
+        <v>730</v>
+      </c>
+      <c r="I81" s="5">
+        <v>30</v>
+      </c>
+      <c r="J81" s="5">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+      <c r="R81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H83">
+        <f>SUBTOTAL(9,H3:H82)</f>
+        <v>58035</v>
+      </c>
+      <c r="I83">
+        <f t="shared" ref="I83:T83" si="2">SUBTOTAL(9,I3:I82)</f>
+        <v>2180</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="2"/>
+        <v>55855</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="S83">
+        <f t="shared" si="2"/>
+        <v>420</v>
+      </c>
+      <c r="T83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J84">
+        <v>-1600</v>
+      </c>
+      <c r="K84" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I87" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I88" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="J88" s="11">
+        <f>SUM(J82:J86)</f>
+        <v>54255</v>
+      </c>
+      <c r="K88" s="11">
+        <f>R83</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I89" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="J89" s="13">
+        <f>S82</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="14"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I90" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="J90" s="13">
+        <f>T82</f>
+        <v>0</v>
+      </c>
+      <c r="K90" s="14"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I91" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="J91" s="13">
+        <f>U82</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="14"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I92" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="J92" s="13">
+        <f>V82</f>
+        <v>0</v>
+      </c>
+      <c r="K92" s="14"/>
+    </row>
+    <row r="93" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I93" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+    </row>
+    <row r="94" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I94" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+    </row>
+    <row r="95" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+      <c r="I95" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="J95" s="19">
+        <f>SUM(J88:J94)</f>
+        <v>54255</v>
+      </c>
+      <c r="K95" s="19">
+        <f>SUM(K88:K92)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G98" s="2">
+        <v>875</v>
+      </c>
+      <c r="H98" s="2">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2">
+        <f t="shared" ref="I98" si="3">G98-H98</f>
+        <v>875</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:Q81" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368F619-C46A-47D8-9E24-6675DE76E0E5}">
+  <dimension ref="A1:S38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>820</v>
+      </c>
+      <c r="H3" s="5">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F4" s="5">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5">
+        <v>805</v>
+      </c>
+      <c r="H4" s="5">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
+        <f>G4-H4</f>
+        <v>770</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5">
+        <v>745</v>
+      </c>
+      <c r="H5" s="5">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f>G5-H5</f>
+        <v>720</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F6" s="5">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f>-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F7" s="21">
+        <v>6</v>
+      </c>
+      <c r="G7" s="21">
+        <v>650</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="24">
+        <f t="shared" ref="I7:I13" si="0">G7-H7</f>
+        <v>620</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F8" s="5">
+        <v>7</v>
+      </c>
+      <c r="G8" s="5">
+        <v>610</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>820</v>
+      </c>
+      <c r="H9" s="5">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G10" s="5">
+        <v>770</v>
+      </c>
+      <c r="H10" s="5">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G11" s="5">
+        <v>820</v>
+      </c>
+      <c r="H11" s="5">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="5">
+        <v>945</v>
+      </c>
+      <c r="H12" s="5">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G13" s="5">
+        <v>730</v>
+      </c>
+      <c r="H13" s="5">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f>-H14</f>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="5">
+        <v>745</v>
+      </c>
+      <c r="H15" s="5">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f>G15-H15</f>
+        <v>720</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>20</v>
+      </c>
+      <c r="I16" s="23">
+        <f>-H16</f>
+        <v>-20</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <f>H16</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="5">
+        <v>915</v>
+      </c>
+      <c r="H17" s="5">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f>G17-H17</f>
+        <v>890</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1920</v>
+      </c>
+      <c r="H18" s="5">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f>G18-H18</f>
+        <v>1890</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="5">
+        <v>30</v>
+      </c>
+      <c r="H19" s="5">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f>G19-H19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="5">
+        <v>35</v>
+      </c>
+      <c r="H20" s="5">
+        <v>35</v>
+      </c>
+      <c r="I20" s="23">
+        <f>G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f>-H21</f>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>755</v>
+      </c>
+      <c r="H22" s="5">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f>G22-H22</f>
+        <v>730</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1890</v>
+      </c>
+      <c r="F23" s="5">
+        <v>4</v>
+      </c>
+      <c r="G23" s="5">
+        <v>815</v>
+      </c>
+      <c r="H23" s="5">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f>G23-H23</f>
+        <v>790</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>1891</v>
+      </c>
+      <c r="F24" s="5">
+        <v>12</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>45</v>
+      </c>
+      <c r="I24" s="23">
+        <f>G24-H24</f>
+        <v>-45</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <f>H24</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <f t="shared" ref="G26:S26" si="1">SUBTOTAL(9,G3:G25)</f>
+        <v>12930</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>635</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>12295</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H31" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I31" s="11">
+        <f>SUM(I25:I29)</f>
+        <v>12295</v>
+      </c>
+      <c r="J31" s="11">
+        <f>Q26</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H32" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I32" s="13">
+        <f>R25</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H33" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I33" s="13">
+        <f>S25</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H34" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I34" s="13">
+        <f>T25</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H35" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I35" s="13">
+        <f>U25</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="8:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H36" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="8:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H37" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+    </row>
+    <row r="38" spans="8:10" ht="21" x14ac:dyDescent="0.35">
+      <c r="H38" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I38" s="19">
+        <f>SUM(I31:I37)</f>
+        <v>12295</v>
+      </c>
+      <c r="J38" s="19">
+        <f>SUM(J31:J35)</f>
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P24" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6909427-7650-467B-B326-121C8B19943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8211443-C656-45BF-B25B-6A4E833EC08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="13" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="14" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="14-3" sheetId="12" r:id="rId12"/>
     <sheet name="16-3" sheetId="13" r:id="rId13"/>
     <sheet name="17-3" sheetId="14" r:id="rId14"/>
+    <sheet name="18-3" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'10-3'!$A$2:$Q$37</definedName>
@@ -36,6 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'14-3'!$A$2:$Q$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-3'!$A$2:$Q$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'17-3'!$A$2:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'18-3'!$A$2:$P$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2-3'!$A$2:$Q$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4-3'!$A$2:$Q$47</definedName>
@@ -63,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="1894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="1898">
   <si>
     <t>THU 2</t>
   </si>
@@ -5745,6 +5747,18 @@
   </si>
   <si>
     <t>NGAY 17-3</t>
+  </si>
+  <si>
+    <t>T4.18.3.2026</t>
+  </si>
+  <si>
+    <t>16-03-2026</t>
+  </si>
+  <si>
+    <t>kh ck 750</t>
+  </si>
+  <si>
+    <t>532/3/6 kinh duong vuong</t>
   </si>
 </sst>
 </file>
@@ -21576,6 +21590,1260 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FA3E6-5335-46FB-860A-11F21DF4CA9C}">
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>820</v>
+      </c>
+      <c r="H3" s="5">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F4" s="5">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5">
+        <v>805</v>
+      </c>
+      <c r="H4" s="5">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
+        <f>G4-H4</f>
+        <v>770</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5">
+        <v>745</v>
+      </c>
+      <c r="H5" s="5">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f>G5-H5</f>
+        <v>720</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F6" s="5">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f>-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F7" s="21">
+        <v>6</v>
+      </c>
+      <c r="G7" s="21">
+        <v>650</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="24">
+        <f t="shared" ref="I7:I13" si="0">G7-H7</f>
+        <v>620</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F8" s="5">
+        <v>7</v>
+      </c>
+      <c r="G8" s="5">
+        <v>610</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>820</v>
+      </c>
+      <c r="H9" s="5">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G10" s="5">
+        <v>770</v>
+      </c>
+      <c r="H10" s="5">
+        <v>30</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G11" s="5">
+        <v>820</v>
+      </c>
+      <c r="H11" s="5">
+        <v>30</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="5">
+        <v>945</v>
+      </c>
+      <c r="H12" s="5">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G13" s="5">
+        <v>730</v>
+      </c>
+      <c r="H13" s="5">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23">
+        <f>-H14</f>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="5">
+        <v>745</v>
+      </c>
+      <c r="H15" s="5">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f>G15-H15</f>
+        <v>720</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>20</v>
+      </c>
+      <c r="I16" s="23">
+        <f>-H16</f>
+        <v>-20</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <f>H16</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="5">
+        <v>915</v>
+      </c>
+      <c r="H17" s="5">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f>G17-H17</f>
+        <v>890</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1920</v>
+      </c>
+      <c r="H18" s="5">
+        <v>30</v>
+      </c>
+      <c r="I18" s="23">
+        <f>G18-H18</f>
+        <v>1890</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="5">
+        <v>30</v>
+      </c>
+      <c r="H19" s="5">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f>G19-H19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="5">
+        <v>35</v>
+      </c>
+      <c r="H20" s="5">
+        <v>35</v>
+      </c>
+      <c r="I20" s="23">
+        <f>G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>25</v>
+      </c>
+      <c r="I21" s="23">
+        <f>-H21</f>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>755</v>
+      </c>
+      <c r="H22" s="5">
+        <v>25</v>
+      </c>
+      <c r="I22" s="23">
+        <f>G22-H22</f>
+        <v>730</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1890</v>
+      </c>
+      <c r="F23" s="5">
+        <v>4</v>
+      </c>
+      <c r="G23" s="5">
+        <v>815</v>
+      </c>
+      <c r="H23" s="5">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f>G23-H23</f>
+        <v>790</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>1891</v>
+      </c>
+      <c r="F24" s="5">
+        <v>12</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>45</v>
+      </c>
+      <c r="I24" s="23">
+        <f>G24-H24</f>
+        <v>-45</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>1867</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <f>H24</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <f t="shared" ref="G26:S26" si="1">SUBTOTAL(9,G3:G25)</f>
+        <v>12930</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>635</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>12295</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H31" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I31" s="11">
+        <f>SUM(I25:I29)</f>
+        <v>12295</v>
+      </c>
+      <c r="J31" s="11">
+        <f>Q26</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H32" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I32" s="13">
+        <f>R25</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H33" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I33" s="13">
+        <f>S25</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H34" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I34" s="13">
+        <f>T25</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H35" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I35" s="13">
+        <f>U25</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H36" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H37" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+    </row>
+    <row r="38" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="H38" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I38" s="19">
+        <f>SUM(I31:I37)</f>
+        <v>12295</v>
+      </c>
+      <c r="J38" s="19">
+        <f>SUM(J31:J35)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F41" s="2">
+        <v>750</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" ref="H41" si="2">F41-G41</f>
+        <v>750</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P24" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DCD748-5697-4B88-A98D-03D4890B00B5}">
   <dimension ref="A1:S63"/>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8211443-C656-45BF-B25B-6A4E833EC08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A39F124-B57A-4BAF-A501-5F19BF2E5EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="14" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="16" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,8 @@
     <sheet name="16-3" sheetId="13" r:id="rId13"/>
     <sheet name="17-3" sheetId="14" r:id="rId14"/>
     <sheet name="18-3" sheetId="15" r:id="rId15"/>
+    <sheet name="19-3" sheetId="16" r:id="rId16"/>
+    <sheet name="20-3" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'10-3'!$A$2:$Q$37</definedName>
@@ -37,7 +39,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'14-3'!$A$2:$Q$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'16-3'!$A$2:$Q$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'17-3'!$A$2:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'18-3'!$A$2:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'18-3'!$A$2:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'19-3'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'20-3'!$A$2:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2-3'!$A$2:$Q$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4-3'!$A$2:$Q$47</definedName>
@@ -65,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="1898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6543" uniqueCount="2116">
   <si>
     <t>THU 2</t>
   </si>
@@ -5759,6 +5763,660 @@
   </si>
   <si>
     <t>532/3/6 kinh duong vuong</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD002716</t>
+  </si>
+  <si>
+    <t>Lavida Plus, Nguyễn Văn Linh, Tân Phong</t>
+  </si>
+  <si>
+    <t>AT 18-03</t>
+  </si>
+  <si>
+    <t>18-03-2026</t>
+  </si>
+  <si>
+    <t>HD002625</t>
+  </si>
+  <si>
+    <t>Chocopie Nguyen</t>
+  </si>
+  <si>
+    <t>HD002660</t>
+  </si>
+  <si>
+    <t>2 đường 22 phường long bình</t>
+  </si>
+  <si>
+    <t>Phương Đào</t>
+  </si>
+  <si>
+    <t>HD002836</t>
+  </si>
+  <si>
+    <t>100/1 B khu phố1, đường Tân thới nhất 11,phường Tân thới nhất</t>
+  </si>
+  <si>
+    <t>W3235</t>
+  </si>
+  <si>
+    <t>HD002687</t>
+  </si>
+  <si>
+    <t>Địa chỉ: 375 tân thới hiệp 21, Tổ 3,Kp3 ( nhớ gỗ đủ)</t>
+  </si>
+  <si>
+    <t>Thanh Tiên</t>
+  </si>
+  <si>
+    <t>HD002513</t>
+  </si>
+  <si>
+    <t>54/17b tô ngọc vân, Thạnh xuân</t>
+  </si>
+  <si>
+    <t>Võ Thu Hà</t>
+  </si>
+  <si>
+    <t>HD002809</t>
+  </si>
+  <si>
+    <t>262/15 lũy bán bích, hòa thạch</t>
+  </si>
+  <si>
+    <t>PUNLORK</t>
+  </si>
+  <si>
+    <t>Xe Phy Phy</t>
+  </si>
+  <si>
+    <t>thu hộ shop</t>
+  </si>
+  <si>
+    <t>Ly Na</t>
+  </si>
+  <si>
+    <t>HD002697</t>
+  </si>
+  <si>
+    <t>98 vũ tông phan, p bình trưng</t>
+  </si>
+  <si>
+    <t>Pé Py</t>
+  </si>
+  <si>
+    <t>HD002724</t>
+  </si>
+  <si>
+    <t>47 bùi đình tuý, P14</t>
+  </si>
+  <si>
+    <t>Ngọc Lan</t>
+  </si>
+  <si>
+    <t>HD002643</t>
+  </si>
+  <si>
+    <t>13 mai xuân thưởng, p11</t>
+  </si>
+  <si>
+    <t>lindsiepham</t>
+  </si>
+  <si>
+    <t>HD002689</t>
+  </si>
+  <si>
+    <t>landmark 5b vinhomes central park</t>
+  </si>
+  <si>
+    <t>VICKY TRAN</t>
+  </si>
+  <si>
+    <t>127/17 bình lợi p13</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>May Oo (Isabella)</t>
+  </si>
+  <si>
+    <t>494/1/12 le quang dinh,P1</t>
+  </si>
+  <si>
+    <t>Cherry Nguyễn</t>
+  </si>
+  <si>
+    <t>HD002837</t>
+  </si>
+  <si>
+    <t>66 hùng vương p1</t>
+  </si>
+  <si>
+    <t>Ngọc Trương</t>
+  </si>
+  <si>
+    <t>HD002835</t>
+  </si>
+  <si>
+    <t>462 phan xích long p2</t>
+  </si>
+  <si>
+    <t>Ín Nile</t>
+  </si>
+  <si>
+    <t>HD002700</t>
+  </si>
+  <si>
+    <t>429/1 nguyễn kiệm p9</t>
+  </si>
+  <si>
+    <t>Jenny Tran</t>
+  </si>
+  <si>
+    <t>HD002603</t>
+  </si>
+  <si>
+    <t>737/1C Lạc Long Quân F10</t>
+  </si>
+  <si>
+    <t>Tiên</t>
+  </si>
+  <si>
+    <t>HD002831</t>
+  </si>
+  <si>
+    <t>Toà A2 chung cư gia hoà</t>
+  </si>
+  <si>
+    <t>19-03-2026</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes Grand park, phường long bình</t>
+  </si>
+  <si>
+    <t>AT 19-03</t>
+  </si>
+  <si>
+    <t>Trinh</t>
+  </si>
+  <si>
+    <t>HD003016</t>
+  </si>
+  <si>
+    <t>105 lý phục man bình thuận</t>
+  </si>
+  <si>
+    <t>kh ck 480</t>
+  </si>
+  <si>
+    <t>Jang Milk</t>
+  </si>
+  <si>
+    <t>HD003133</t>
+  </si>
+  <si>
+    <t>118 Huỳnh Tấn Phát Tân Thuận Tây</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>HD003156</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bừu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
+    <t>Thảo Ly Nguyễn</t>
+  </si>
+  <si>
+    <t>HD002894</t>
+  </si>
+  <si>
+    <t>35/4 đường Nguyễn thị búp phường hiệp thành</t>
+  </si>
+  <si>
+    <t>Thanh Mây</t>
+  </si>
+  <si>
+    <t>HD003139</t>
+  </si>
+  <si>
+    <t>70G hẻm F1 xã Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>binh chanh</t>
+  </si>
+  <si>
+    <t>Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD003079</t>
+  </si>
+  <si>
+    <t>Số 4 đường số 22 khu dân cư bình hưng xã binh hưng</t>
+  </si>
+  <si>
+    <t>Vòng Hồng Tuyền</t>
+  </si>
+  <si>
+    <t>HD002956</t>
+  </si>
+  <si>
+    <t>125/34 tây lân, phường bình trị động a</t>
+  </si>
+  <si>
+    <t>Ngọc Sương</t>
+  </si>
+  <si>
+    <t>HD002909</t>
+  </si>
+  <si>
+    <t>704/44 hương lộ 2, bình trị đông a</t>
+  </si>
+  <si>
+    <t>Doan Sam</t>
+  </si>
+  <si>
+    <t>HD002953</t>
+  </si>
+  <si>
+    <t>170/9a đường Trưng Vương 3, Ấp 61, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>hoc mon</t>
+  </si>
+  <si>
+    <t>Nhung Xuxy</t>
+  </si>
+  <si>
+    <t>HD003018</t>
+  </si>
+  <si>
+    <t>2/11 thiên phước phường 9</t>
+  </si>
+  <si>
+    <t>Anh Nhi Phương hoa (ah ni )</t>
+  </si>
+  <si>
+    <t>HD003092</t>
+  </si>
+  <si>
+    <t>007 LÔ B, Đường Cô, C/C Tây Thanh, P. Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Kim Liên</t>
+  </si>
+  <si>
+    <t>HD003047</t>
+  </si>
+  <si>
+    <t>hẻm 10/4 tên quý</t>
+  </si>
+  <si>
+    <t>Lâm Tiên</t>
+  </si>
+  <si>
+    <t>HD003140</t>
+  </si>
+  <si>
+    <t>961 Hậu Giang, Lô D, Chung Cư An Phú</t>
+  </si>
+  <si>
+    <t>Nuong Huynh</t>
+  </si>
+  <si>
+    <t>HD002920</t>
+  </si>
+  <si>
+    <t>67 mai chí thọ phường an phú Cc lexington block B</t>
+  </si>
+  <si>
+    <t>Bằng Bing</t>
+  </si>
+  <si>
+    <t>HD002901</t>
+  </si>
+  <si>
+    <t>Landmark 5, Vinhome central park, F22</t>
+  </si>
+  <si>
+    <t>Kim Anh</t>
+  </si>
+  <si>
+    <t>HD002992</t>
+  </si>
+  <si>
+    <t>124/83/1 xô viết nghệ tĩnh p21</t>
+  </si>
+  <si>
+    <t>401 quang trung f10</t>
+  </si>
+  <si>
+    <t>Võ Ngọc Tường Vy</t>
+  </si>
+  <si>
+    <t>HD003121</t>
+  </si>
+  <si>
+    <t>14/11 bàu bàng, p13</t>
+  </si>
+  <si>
+    <t>Mr Thế</t>
+  </si>
+  <si>
+    <t>27/5 Quách Văn Tuấn, F12</t>
+  </si>
+  <si>
+    <t>Phương Trang</t>
+  </si>
+  <si>
+    <t>HD003015</t>
+  </si>
+  <si>
+    <t>189b/a29 cống quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>Danh Hồng</t>
+  </si>
+  <si>
+    <t>HD003149</t>
+  </si>
+  <si>
+    <t>33 nguyễn văn giai p đakao</t>
+  </si>
+  <si>
+    <t>Lý Minh Đức - fb Jolies Le</t>
+  </si>
+  <si>
+    <t>HD003157</t>
+  </si>
+  <si>
+    <t>581 tran hung đạo</t>
+  </si>
+  <si>
+    <t>Lien Thuy</t>
+  </si>
+  <si>
+    <t>HD003107</t>
+  </si>
+  <si>
+    <t>151 nguyễn định chiều p.xuân hoà</t>
+  </si>
+  <si>
+    <t>Đào Minh Ánh</t>
+  </si>
+  <si>
+    <t>HD003132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91/2a, Nguyễn Khoái, Phường 1 </t>
+  </si>
+  <si>
+    <t>Nguyễn LyNa</t>
+  </si>
+  <si>
+    <t>HD003104</t>
+  </si>
+  <si>
+    <t>Chung cư số 1 tôn thất thuyết p1</t>
+  </si>
+  <si>
+    <t>kh ck 1525</t>
+  </si>
+  <si>
+    <t>NGUYÊN NGUYÊN</t>
+  </si>
+  <si>
+    <t>12 TÔN ĐẢN P13</t>
+  </si>
+  <si>
+    <t>kim ngân</t>
+  </si>
+  <si>
+    <t>HD002974</t>
+  </si>
+  <si>
+    <t>162 đường số 3 xã bình hưng</t>
+  </si>
+  <si>
+    <t>Hoàng Kim</t>
+  </si>
+  <si>
+    <t>HD002898</t>
+  </si>
+  <si>
+    <t>162 đường số 3, Trung Sơn, Bình Hưng</t>
+  </si>
+  <si>
+    <t>Linh</t>
+  </si>
+  <si>
+    <t>B12-03 Block B, botanica premier, 112 hồng hà p2</t>
+  </si>
+  <si>
+    <t>T5.19.3.2026</t>
+  </si>
+  <si>
+    <t>Bình Bee</t>
+  </si>
+  <si>
+    <t>HD003301</t>
+  </si>
+  <si>
+    <t>133 đỗ xuân hợp, phường phước long B</t>
+  </si>
+  <si>
+    <t>20-03-2026</t>
+  </si>
+  <si>
+    <t>QUÝ KHÁCH VUI LÒNG</t>
+  </si>
+  <si>
+    <t>Số nhà 97A, đường 22, phường phước long</t>
+  </si>
+  <si>
+    <t>Ng T Thi</t>
+  </si>
+  <si>
+    <t>HD003004</t>
+  </si>
+  <si>
+    <t>1135/17/28 huỳn tấn phát</t>
+  </si>
+  <si>
+    <t>AT 20-03</t>
+  </si>
+  <si>
+    <t>Người Nhân Kim Loan (Ivybee)</t>
+  </si>
+  <si>
+    <t>HD003237</t>
+  </si>
+  <si>
+    <t>127/48/30 Âu Cơ, phường 14</t>
+  </si>
+  <si>
+    <t>W2886</t>
+  </si>
+  <si>
+    <t>HD003205</t>
+  </si>
+  <si>
+    <t>Địa chỉ: 375 tân thới hiệp 21, Tổ 3,Kp3 ( nhớ gõ đủ) Số kho : 0325267896 ( nhớ ghi mã khách hàng )</t>
+  </si>
+  <si>
+    <t>Nguyễn Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD003296</t>
+  </si>
+  <si>
+    <t>67 duong 14 khu lovera khang điền phong phú 4</t>
+  </si>
+  <si>
+    <t>Misa Trần</t>
+  </si>
+  <si>
+    <t>HD003216</t>
+  </si>
+  <si>
+    <t>27 Đường Số 1 tân tạo a</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Phương</t>
+  </si>
+  <si>
+    <t>HD003361</t>
+  </si>
+  <si>
+    <t>Sunrise riverside tháp H Đường Nguyễn hữu thọ</t>
+  </si>
+  <si>
+    <t>HD003300</t>
+  </si>
+  <si>
+    <t>10 Nguyễn Thái Học, phường Tân Thành</t>
+  </si>
+  <si>
+    <t>HD003241</t>
+  </si>
+  <si>
+    <t>Bẹp</t>
+  </si>
+  <si>
+    <t>HD003353</t>
+  </si>
+  <si>
+    <t>Lanmark 5-vinhome central park, Nguyễn hữu cảnh- thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>HÀ VY</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang long, p13</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>tên Xuân ( nhan gium Nhi Doan)</t>
+  </si>
+  <si>
+    <t>HD003330</t>
+  </si>
+  <si>
+    <t>33/9 Quách Văn Tuấn phuong 12</t>
+  </si>
+  <si>
+    <t>Phạm Thị Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD003288</t>
+  </si>
+  <si>
+    <t>Block B Chung Cư Urban Green, Đường Số 6, Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Ánh Hồng</t>
+  </si>
+  <si>
+    <t>HD003225</t>
+  </si>
+  <si>
+    <t>82/28 đường số 2 phường hiệp bình phước</t>
+  </si>
+  <si>
+    <t>thu đuc</t>
+  </si>
+  <si>
+    <t>Như Quỳnh</t>
+  </si>
+  <si>
+    <t>HD003309</t>
+  </si>
+  <si>
+    <t>32 nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>HD003245</t>
+  </si>
+  <si>
+    <t>Chị Oanh fb Ivy Trần</t>
+  </si>
+  <si>
+    <t>HD003191</t>
+  </si>
+  <si>
+    <t>Toà nhà Takashimaya (cổng giao hàng) _ Số 92 – 94 Nam Kỳ Khởi Nghĩa, Phường Bến Nghé</t>
+  </si>
+  <si>
+    <t>Diệu Ngọc</t>
+  </si>
+  <si>
+    <t>HD003362</t>
+  </si>
+  <si>
+    <t>40e ngô đức kể,bến nghé</t>
+  </si>
+  <si>
+    <t>Mai Nhung</t>
+  </si>
+  <si>
+    <t>HD003167</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn, P1</t>
+  </si>
+  <si>
+    <t>borameyyy 015738168</t>
+  </si>
+  <si>
+    <t>HD003117</t>
+  </si>
+  <si>
+    <t>363-365-367, 363 Đ. Hùng Vương, Phường 9</t>
+  </si>
+  <si>
+    <t>Kim An</t>
+  </si>
+  <si>
+    <t>HD003281</t>
+  </si>
+  <si>
+    <t>Bệnh viện Emcas 14/27 Hoàng Dư Khương, f12</t>
+  </si>
+  <si>
+    <t>thu thu</t>
+  </si>
+  <si>
+    <t>HD003359</t>
+  </si>
+  <si>
+    <t>165/1 bạch đằng p2</t>
+  </si>
+  <si>
+    <t>kh ck 1450</t>
+  </si>
+  <si>
+    <t>NGAY 20-3</t>
+  </si>
+  <si>
+    <t>NGAY 19-3</t>
+  </si>
+  <si>
+    <t>NGAY 18-3</t>
+  </si>
+  <si>
+    <t>kh ck 1320</t>
   </si>
 </sst>
 </file>
@@ -5913,7 +6571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5961,6 +6619,15 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10069,8 +10736,8 @@
         <v>319</v>
       </c>
       <c r="J86" s="13">
-        <f>S79</f>
-        <v>0</v>
+        <f>S80</f>
+        <v>480</v>
       </c>
       <c r="K86" s="14"/>
     </row>
@@ -10124,7 +10791,7 @@
       </c>
       <c r="J92" s="19">
         <f>SUM(J85:J91)</f>
-        <v>45754</v>
+        <v>46234</v>
       </c>
       <c r="K92" s="19">
         <f>SUM(K85:K89)</f>
@@ -12509,8 +13176,8 @@
         <v>319</v>
       </c>
       <c r="J52" s="13">
-        <f>S45</f>
-        <v>0</v>
+        <f>S46</f>
+        <v>220</v>
       </c>
       <c r="K52" s="14"/>
     </row>
@@ -12564,7 +13231,7 @@
       </c>
       <c r="J58" s="19">
         <f>SUM(J51:J57)</f>
-        <v>22470</v>
+        <v>22690</v>
       </c>
       <c r="K58" s="19">
         <f>SUM(K51:K55)</f>
@@ -14568,8 +15235,8 @@
         <v>319</v>
       </c>
       <c r="J49" s="13">
-        <f>S42</f>
-        <v>0</v>
+        <f>S43</f>
+        <v>85</v>
       </c>
       <c r="K49" s="14"/>
     </row>
@@ -14623,7 +15290,7 @@
       </c>
       <c r="J55" s="19">
         <f>SUM(J48:J54)</f>
-        <v>27175</v>
+        <v>27260</v>
       </c>
       <c r="K55" s="19">
         <f>SUM(K48:K52)</f>
@@ -16227,8 +16894,8 @@
         <v>319</v>
       </c>
       <c r="J40" s="13">
-        <f>S33</f>
-        <v>0</v>
+        <f>S34</f>
+        <v>215</v>
       </c>
       <c r="K40" s="14"/>
     </row>
@@ -16282,7 +16949,7 @@
       </c>
       <c r="J46" s="19">
         <f>SUM(J39:J45)</f>
-        <v>15985</v>
+        <v>16200</v>
       </c>
       <c r="K46" s="19">
         <f>SUM(K39:K43)</f>
@@ -20265,8 +20932,8 @@
         <v>319</v>
       </c>
       <c r="J89" s="13">
-        <f>S82</f>
-        <v>0</v>
+        <f>S83</f>
+        <v>420</v>
       </c>
       <c r="K89" s="14"/>
     </row>
@@ -20320,7 +20987,7 @@
       </c>
       <c r="J95" s="19">
         <f>SUM(J88:J94)</f>
-        <v>54255</v>
+        <v>54675</v>
       </c>
       <c r="K95" s="19">
         <f>SUM(K88:K92)</f>
@@ -21522,8 +22189,8 @@
         <v>319</v>
       </c>
       <c r="I32" s="13">
-        <f>R25</f>
-        <v>0</v>
+        <f>R26</f>
+        <v>145</v>
       </c>
       <c r="J32" s="14"/>
     </row>
@@ -21577,7 +22244,7 @@
       </c>
       <c r="I38" s="19">
         <f>SUM(I31:I37)</f>
-        <v>12295</v>
+        <v>12440</v>
       </c>
       <c r="J38" s="19">
         <f>SUM(J31:J35)</f>
@@ -21592,7 +22259,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FA3E6-5335-46FB-860A-11F21DF4CA9C}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -21601,14 +22268,15 @@
     <col min="5" max="5" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>330</v>
+        <v>489</v>
       </c>
       <c r="C1" t="s">
-        <v>1893</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21667,37 +22335,38 @@
         <v>1825</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1826</v>
+        <v>1898</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1827</v>
+        <v>1899</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1865</v>
+        <v>1900</v>
       </c>
       <c r="F3" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="5">
-        <v>820</v>
+        <v>670</v>
       </c>
       <c r="H3" s="5">
         <v>30</v>
       </c>
       <c r="I3" s="23">
-        <f>G3-H3</f>
-        <v>790</v>
+        <v>640</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>1866</v>
+        <v>1901</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>1867</v>
-      </c>
-      <c r="M3" s="5"/>
+        <v>1902</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>350</v>
+      </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -21706,42 +22375,43 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1829</v>
-      </c>
-      <c r="D4" s="5"/>
+        <v>1898</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1903</v>
+      </c>
       <c r="E4" s="5" t="s">
-        <v>1868</v>
+        <v>1900</v>
       </c>
       <c r="F4" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="5">
-        <v>805</v>
+        <v>350</v>
       </c>
       <c r="H4" s="5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I4" s="23">
-        <f>G4-H4</f>
-        <v>770</v>
+        <v>350</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>1866</v>
+        <v>1901</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>1867</v>
-      </c>
-      <c r="M4" s="5"/>
+        <v>1902</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>350</v>
+      </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -21755,35 +22425,34 @@
         <v>1825</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1830</v>
+        <v>1904</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1831</v>
+        <v>1905</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1869</v>
+        <v>1906</v>
       </c>
       <c r="F5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5">
-        <v>745</v>
+        <v>670</v>
       </c>
       <c r="H5" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I5" s="23">
-        <f>G5-H5</f>
-        <v>720</v>
+        <v>640</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -21794,40 +22463,39 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1832</v>
-      </c>
-      <c r="D6" s="5"/>
+        <v>1907</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1908</v>
+      </c>
       <c r="E6" s="5" t="s">
-        <v>1871</v>
+        <v>1909</v>
       </c>
       <c r="F6" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="H6" s="5">
         <v>30</v>
       </c>
       <c r="I6" s="23">
-        <f>-H6</f>
-        <v>-30</v>
+        <v>700</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -21836,46 +22504,41 @@
       <c r="Q6">
         <v>1</v>
       </c>
-      <c r="R6">
-        <f>H6</f>
-        <v>30</v>
-      </c>
     </row>
     <row r="7" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A7" s="21"/>
       <c r="B7" s="21" t="s">
         <v>1825</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D7" s="21"/>
+        <v>1910</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>1911</v>
+      </c>
       <c r="E7" s="21" t="s">
-        <v>1872</v>
+        <v>1912</v>
       </c>
       <c r="F7" s="21">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" s="21">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="H7" s="21">
         <v>30</v>
       </c>
       <c r="I7" s="24">
-        <f t="shared" ref="I7:I13" si="0">G7-H7</f>
-        <v>620</v>
+        <v>-30</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K7" s="21" t="s">
         <v>25</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
@@ -21884,6 +22547,10 @@
       <c r="Q7" s="22">
         <v>1</v>
       </c>
+      <c r="R7" s="22">
+        <f>H7</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
@@ -21891,43 +22558,48 @@
         <v>1825</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1834</v>
+        <v>1913</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1835</v>
+        <v>1914</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1873</v>
+        <v>1915</v>
       </c>
       <c r="F8" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G8" s="5">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
         <v>30</v>
       </c>
       <c r="I8" s="23">
-        <f t="shared" si="0"/>
-        <v>580</v>
+        <v>-30</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>1867</v>
-      </c>
-      <c r="M8" s="5"/>
+        <v>1902</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>472</v>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8">
         <v>1</v>
       </c>
+      <c r="R8" s="22">
+        <f>H8</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
@@ -21935,35 +22607,34 @@
         <v>1825</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1836</v>
+        <v>1916</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1837</v>
+        <v>1917</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1874</v>
-      </c>
-      <c r="F9" s="5">
-        <v>7</v>
+        <v>1918</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G9" s="5">
-        <v>820</v>
+        <v>755</v>
       </c>
       <c r="H9" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I9" s="23">
-        <f t="shared" si="0"/>
-        <v>790</v>
+        <v>730</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -21974,42 +22645,43 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
+      <c r="A10" s="5" t="s">
+        <v>1828</v>
+      </c>
       <c r="B10" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1838</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>1839</v>
-      </c>
+        <v>1919</v>
+      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>1875</v>
+        <v>1920</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1876</v>
+        <v>104</v>
       </c>
       <c r="G10" s="5">
-        <v>770</v>
+        <v>1860</v>
       </c>
       <c r="H10" s="5">
         <v>30</v>
       </c>
       <c r="I10" s="23">
-        <f t="shared" si="0"/>
-        <v>740</v>
+        <v>1830</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>1870</v>
+        <v>1901</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>1867</v>
-      </c>
-      <c r="M10" s="5"/>
+        <v>1902</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>1921</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -22023,35 +22695,34 @@
         <v>1825</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1840</v>
+        <v>1922</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1841</v>
+        <v>1923</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1877</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>1876</v>
+        <v>1924</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
       </c>
       <c r="G11" s="5">
-        <v>820</v>
+        <v>870</v>
       </c>
       <c r="H11" s="5">
         <v>30</v>
       </c>
       <c r="I11" s="23">
-        <f t="shared" si="0"/>
-        <v>790</v>
+        <v>840</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1870</v>
+        <v>25</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -22067,35 +22738,34 @@
         <v>1825</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1842</v>
+        <v>1925</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1843</v>
+        <v>1926</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1878</v>
+        <v>1927</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5">
-        <v>945</v>
+        <v>1630</v>
       </c>
       <c r="H12" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I12" s="23">
-        <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1610</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>1870</v>
+        <v>25</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -22111,35 +22781,34 @@
         <v>1825</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1844</v>
+        <v>1928</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1845</v>
+        <v>1929</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1879</v>
+        <v>1930</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>607</v>
+        <v>64</v>
       </c>
       <c r="G13" s="5">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="H13" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I13" s="23">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>-20</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>1870</v>
+        <v>25</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -22148,6 +22817,10 @@
       <c r="Q13">
         <v>1</v>
       </c>
+      <c r="R13" s="22">
+        <f>H13</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
@@ -22155,35 +22828,34 @@
         <v>1825</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1846</v>
+        <v>1931</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1847</v>
+        <v>1932</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1880</v>
+        <v>1933</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>607</v>
+        <v>64</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="H14" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I14" s="23">
-        <f>-H14</f>
-        <v>-25</v>
+        <v>790</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>1870</v>
+        <v>25</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -22192,37 +22864,32 @@
       <c r="Q14">
         <v>1</v>
       </c>
-      <c r="R14">
-        <f>H14</f>
-        <v>25</v>
-      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="5" t="s">
+        <v>1828</v>
+      </c>
       <c r="B15" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1848</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>1849</v>
-      </c>
+        <v>1934</v>
+      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>1881</v>
+        <v>1935</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G15" s="5">
-        <v>745</v>
+        <v>30</v>
       </c>
       <c r="H15" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I15" s="23">
-        <f>G15-H15</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>25</v>
@@ -22231,7 +22898,7 @@
         <v>25</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -22242,32 +22909,31 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="5" t="s">
+        <v>1828</v>
+      </c>
       <c r="B16" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>1851</v>
-      </c>
+        <v>1936</v>
+      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>1882</v>
+        <v>1937</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G16" s="5">
+        <v>30</v>
+      </c>
+      <c r="H16" s="5">
+        <v>30</v>
+      </c>
+      <c r="I16" s="23">
         <v>0</v>
       </c>
-      <c r="H16" s="5">
-        <v>20</v>
-      </c>
-      <c r="I16" s="23">
-        <f>-H16</f>
-        <v>-20</v>
-      </c>
       <c r="J16" s="5" t="s">
         <v>25</v>
       </c>
@@ -22275,7 +22941,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -22284,37 +22950,32 @@
       <c r="Q16">
         <v>1</v>
       </c>
-      <c r="R16">
-        <f>H16</f>
-        <v>20</v>
-      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
+      <c r="A17" s="5" t="s">
+        <v>1828</v>
+      </c>
       <c r="B17" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>1853</v>
-      </c>
+        <v>1938</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>1883</v>
+        <v>1939</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>76</v>
       </c>
       <c r="G17" s="5">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="23">
-        <f>G17-H17</f>
-        <v>890</v>
+        <v>-30</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>25</v>
@@ -22323,7 +22984,7 @@
         <v>25</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -22332,42 +22993,45 @@
       <c r="Q17">
         <v>1</v>
       </c>
+      <c r="R17" s="22">
+        <f>H17</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>1940</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1941</v>
+      </c>
       <c r="E18" s="5" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>76</v>
+        <v>1942</v>
+      </c>
+      <c r="F18" s="5">
+        <v>10</v>
       </c>
       <c r="G18" s="5">
-        <v>1920</v>
+        <v>1455</v>
       </c>
       <c r="H18" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I18" s="23">
-        <f>G18-H18</f>
-        <v>1890</v>
+        <v>1430</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>25</v>
+        <v>1888</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -22378,40 +23042,39 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1855</v>
-      </c>
-      <c r="D19" s="5"/>
+        <v>1943</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1944</v>
+      </c>
       <c r="E19" s="5" t="s">
-        <v>1885</v>
+        <v>1945</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="G19" s="5">
-        <v>30</v>
+        <v>660</v>
       </c>
       <c r="H19" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I19" s="23">
-        <f>G19-H19</f>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>25</v>
+        <v>1888</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -22422,40 +23085,39 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>1828</v>
-      </c>
+      <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>1856</v>
-      </c>
-      <c r="D20" s="5"/>
+        <v>1946</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1947</v>
+      </c>
       <c r="E20" s="5" t="s">
-        <v>1886</v>
+        <v>1948</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="G20" s="5">
-        <v>35</v>
+        <v>600</v>
       </c>
       <c r="H20" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I20" s="23">
-        <f>G20-H20</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>25</v>
+        <v>1888</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
@@ -22471,26 +23133,25 @@
         <v>1825</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1857</v>
+        <v>1949</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1858</v>
+        <v>1950</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1887</v>
+        <v>1951</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="H21" s="5">
         <v>25</v>
       </c>
       <c r="I21" s="23">
-        <f>-H21</f>
-        <v>-25</v>
+        <v>850</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>1888</v>
@@ -22499,7 +23160,7 @@
         <v>25</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>1867</v>
+        <v>1902</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -22508,100 +23169,1209 @@
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="R21">
-        <f>H21</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <f t="shared" ref="G23:S23" si="0">SUBTOTAL(9,G3:G22)</f>
+        <v>11995</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>475</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>11520</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I24" s="25"/>
+    </row>
+    <row r="27" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H28" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I28" s="11">
+        <f>SUM(I22:I26)</f>
+        <v>11520</v>
+      </c>
+      <c r="J28" s="11">
+        <f>Q23</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H29" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I29" s="13">
+        <f>R23</f>
+        <v>110</v>
+      </c>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H30" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I30" s="13">
+        <f>S23</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H31" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I31" s="13">
+        <f>T23</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H32" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I32" s="13">
+        <f>U23</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H33" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H34" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+    </row>
+    <row r="35" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="H35" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I35" s="19">
+        <f>SUM(I28:I34)</f>
+        <v>11630</v>
+      </c>
+      <c r="J35" s="19">
+        <f>SUM(J28:J32)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F38" s="2">
+        <v>750</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" ref="H38" si="1">F38-G38</f>
+        <v>750</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P21" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DC3523-A7E3-4CC1-8375-C845D3F25091}">
+  <dimension ref="A1:R51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F3" s="23">
+        <v>9</v>
+      </c>
+      <c r="G3" s="23">
+        <v>870</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>840</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F4" s="23">
+        <v>9</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1625</v>
+      </c>
+      <c r="H4" s="23">
+        <v>35</v>
+      </c>
+      <c r="I4" s="23">
+        <f t="shared" ref="I4:I34" si="0">G4-H4</f>
+        <v>1590</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F5" s="23">
+        <v>6</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="25">
+        <v>1</v>
+      </c>
+      <c r="R5" s="25">
+        <f>H5</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F6" s="23">
+        <v>7</v>
+      </c>
+      <c r="G6" s="23">
+        <v>30</v>
+      </c>
+      <c r="H6" s="23">
+        <v>30</v>
+      </c>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>1961</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F7" s="23">
+        <v>7</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1610</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
+        <v>1580</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F8" s="23">
+        <v>8</v>
+      </c>
+      <c r="G8" s="23">
+        <v>850</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F9" s="23">
+        <v>12</v>
+      </c>
+      <c r="G9" s="23">
+        <v>820</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G10" s="23">
+        <v>745</v>
+      </c>
+      <c r="H10" s="23">
+        <v>35</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G11" s="23">
+        <v>35</v>
+      </c>
+      <c r="H11" s="23">
+        <v>35</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1760</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>1730</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G13" s="23">
+        <v>670</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1986</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>1987</v>
+      </c>
+      <c r="G14" s="23">
+        <v>115</v>
+      </c>
+      <c r="H14" s="23">
+        <v>35</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="23">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="25">
+        <v>1</v>
+      </c>
+      <c r="R15" s="25">
+        <f>H15</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1993</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G16" s="23">
+        <v>885</v>
+      </c>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1995</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G17" s="23">
+        <v>745</v>
+      </c>
+      <c r="H17" s="23">
+        <v>25</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F18" s="23">
+        <v>6</v>
+      </c>
+      <c r="G18" s="23">
+        <v>735</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F19" s="23">
+        <v>2</v>
+      </c>
+      <c r="G19" s="23">
+        <v>890</v>
+      </c>
+      <c r="H19" s="23">
+        <v>30</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>2005</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="23">
+        <v>1450</v>
+      </c>
+      <c r="H20" s="23">
+        <v>20</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="26">
+        <v>20</v>
+      </c>
+      <c r="H21" s="26">
+        <v>20</v>
+      </c>
+      <c r="I21" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>1828</v>
+      </c>
       <c r="B22" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>1860</v>
-      </c>
+        <v>1854</v>
+      </c>
+      <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>1889</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>755</v>
-      </c>
-      <c r="H22" s="5">
-        <v>25</v>
+        <v>2009</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="23">
+        <v>1530</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
       </c>
       <c r="I22" s="23">
-        <f>G22-H22</f>
-        <v>730</v>
+        <f t="shared" si="0"/>
+        <v>1500</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>1888</v>
+        <v>25</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>1867</v>
+        <v>1955</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q22" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>1825</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1861</v>
+        <v>2010</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1862</v>
+        <v>2011</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1890</v>
-      </c>
-      <c r="F23" s="5">
-        <v>4</v>
-      </c>
-      <c r="G23" s="5">
-        <v>815</v>
-      </c>
-      <c r="H23" s="5">
+        <v>2012</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="23">
+        <v>765</v>
+      </c>
+      <c r="H23" s="23">
         <v>25</v>
       </c>
       <c r="I23" s="23">
-        <f>G23-H23</f>
-        <v>790</v>
+        <f t="shared" si="0"/>
+        <v>740</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>1888</v>
+        <v>25</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>1867</v>
+        <v>1955</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>1828</v>
       </c>
@@ -22609,238 +24379,2079 @@
         <v>1825</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>1863</v>
+        <v>2013</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>1891</v>
-      </c>
-      <c r="F24" s="5">
-        <v>12</v>
-      </c>
-      <c r="G24" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="23">
+        <v>30</v>
+      </c>
+      <c r="H24" s="23">
+        <v>30</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="5">
-        <v>45</v>
-      </c>
-      <c r="I24" s="23">
-        <f>G24-H24</f>
-        <v>-45</v>
-      </c>
       <c r="J24" s="5" t="s">
-        <v>1888</v>
+        <v>25</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>1867</v>
+        <v>1955</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <f>H24</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="G26">
-        <f t="shared" ref="G26:S26" si="1">SUBTOTAL(9,G3:G25)</f>
-        <v>12930</v>
-      </c>
-      <c r="H26">
+      <c r="Q24" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23">
+        <v>945</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23">
+        <v>1015</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23">
+        <v>1155</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>1130</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F28" s="23">
+        <v>3</v>
+      </c>
+      <c r="G28" s="23">
+        <v>1455</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F29" s="23">
+        <v>4</v>
+      </c>
+      <c r="G29" s="23">
+        <v>885</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F30" s="23">
+        <v>4</v>
+      </c>
+      <c r="G30" s="23">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23">
+        <v>25</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>2033</v>
+      </c>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="25">
+        <v>1</v>
+      </c>
+      <c r="R30" s="25">
+        <f>H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>2035</v>
+      </c>
+      <c r="F31" s="23">
+        <v>4</v>
+      </c>
+      <c r="G31" s="23">
+        <v>30</v>
+      </c>
+      <c r="H31" s="23">
+        <v>30</v>
+      </c>
+      <c r="I31" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G32" s="23">
+        <v>765</v>
+      </c>
+      <c r="H32" s="23">
+        <v>35</v>
+      </c>
+      <c r="I32" s="23">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G33" s="23">
+        <v>415</v>
+      </c>
+      <c r="H33" s="23">
+        <v>35</v>
+      </c>
+      <c r="I33" s="23">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>2043</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="23">
+        <v>0</v>
+      </c>
+      <c r="H34" s="23">
+        <v>30</v>
+      </c>
+      <c r="I34" s="23">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>1955</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="25">
+        <v>1</v>
+      </c>
+      <c r="R34" s="25">
+        <f>H34</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <f>SUBTOTAL(9,G3:G35)</f>
+        <v>22845</v>
+      </c>
+      <c r="H36">
+        <f t="shared" ref="H36:R36" si="1">SUBTOTAL(9,H3:H35)</f>
+        <v>910</v>
+      </c>
+      <c r="I36">
         <f t="shared" si="1"/>
-        <v>635</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="1"/>
-        <v>12295</v>
-      </c>
-      <c r="J26">
+        <v>21935</v>
+      </c>
+      <c r="J36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26">
+      <c r="K36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26">
+      <c r="L36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M26">
+      <c r="M36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N26">
+      <c r="N36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O26">
+      <c r="O36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P26">
+      <c r="P36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26">
+      <c r="Q36">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="R26">
+        <v>32</v>
+      </c>
+      <c r="R36">
         <f t="shared" si="1"/>
-        <v>145</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="7" t="s">
+        <v>2044</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H41" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I41" s="11">
+        <f>SUM(I35:I39)</f>
+        <v>21935</v>
+      </c>
+      <c r="J41" s="11">
+        <f>Q36</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I42" s="13">
+        <f>R36</f>
+        <v>105</v>
+      </c>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I43" s="13">
+        <f>S36</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H30" s="7" t="s">
-        <v>1894</v>
-      </c>
-      <c r="I30" s="8" t="s">
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I44" s="13">
+        <f>T36</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I45" s="13">
+        <f>U36</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H46" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H47" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="H48" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I48" s="19">
+        <f>SUM(I41:I47)</f>
+        <v>22040</v>
+      </c>
+      <c r="J48" s="19">
+        <f>SUM(J41:J45)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D50" s="27">
+        <v>7</v>
+      </c>
+      <c r="E50" s="27">
+        <v>480</v>
+      </c>
+      <c r="F50" s="27">
+        <v>0</v>
+      </c>
+      <c r="G50" s="27">
+        <f>E50-F50</f>
+        <v>480</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D51" s="27">
+        <v>4</v>
+      </c>
+      <c r="E51" s="27">
+        <v>1525</v>
+      </c>
+      <c r="F51" s="27">
+        <v>0</v>
+      </c>
+      <c r="G51" s="27">
+        <f>E51-F51</f>
+        <v>1525</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{95DC3523-A7E3-4CC1-8375-C845D3F25091}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F168EF-0B24-46A3-87F2-E8254CC1AE4A}">
+  <dimension ref="A1:R44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="21"/>
+      <c r="B3" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F3" s="28">
+        <v>9</v>
+      </c>
+      <c r="G3" s="24">
+        <v>470</v>
+      </c>
+      <c r="H3" s="24">
+        <v>30</v>
+      </c>
+      <c r="I3" s="24">
+        <v>440</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F4" s="28">
+        <v>9</v>
+      </c>
+      <c r="G4" s="24">
+        <v>35</v>
+      </c>
+      <c r="H4" s="24">
+        <v>35</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>1866</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F5" s="28">
+        <v>7</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
+        <v>30</v>
+      </c>
+      <c r="I5" s="24">
+        <v>-30</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>2115</v>
+      </c>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="25">
+        <v>1</v>
+      </c>
+      <c r="R5" s="25"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F6" s="28">
+        <v>11</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24">
+        <v>25</v>
+      </c>
+      <c r="I6" s="24">
+        <v>-25</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="25">
+        <v>1</v>
+      </c>
+      <c r="R6" s="25">
+        <f>H6</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F7" s="28">
+        <v>12</v>
+      </c>
+      <c r="G7" s="24">
+        <v>820</v>
+      </c>
+      <c r="H7" s="24">
+        <v>30</v>
+      </c>
+      <c r="I7" s="24">
+        <v>790</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="20" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G8" s="20">
+        <v>155</v>
+      </c>
+      <c r="H8" s="20">
+        <v>35</v>
+      </c>
+      <c r="I8" s="20">
+        <v>120</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G9" s="24">
+        <v>410</v>
+      </c>
+      <c r="H9" s="24">
+        <v>30</v>
+      </c>
+      <c r="I9" s="24">
+        <v>380</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="G10" s="24">
+        <v>415</v>
+      </c>
+      <c r="H10" s="24">
+        <v>35</v>
+      </c>
+      <c r="I10" s="24">
+        <v>380</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>607</v>
+      </c>
+      <c r="G11" s="24">
+        <v>815</v>
+      </c>
+      <c r="H11" s="24">
+        <v>25</v>
+      </c>
+      <c r="I11" s="24">
+        <v>790</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>2054</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="24">
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <v>20</v>
+      </c>
+      <c r="I12" s="24">
+        <v>-20</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="25">
+        <v>1</v>
+      </c>
+      <c r="R12" s="25">
+        <f>H12</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="24">
+        <v>720</v>
+      </c>
+      <c r="H13" s="24">
+        <v>20</v>
+      </c>
+      <c r="I13" s="24">
+        <v>700</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="24">
+        <v>305</v>
+      </c>
+      <c r="H14" s="24">
+        <v>25</v>
+      </c>
+      <c r="I14" s="24">
+        <v>280</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="24">
+        <v>30</v>
+      </c>
+      <c r="H15" s="24">
+        <v>30</v>
+      </c>
+      <c r="I15" s="24">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="25">
+        <v>1</v>
+      </c>
+      <c r="R15" s="25"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="24">
+        <v>0</v>
+      </c>
+      <c r="H16" s="24">
+        <v>25</v>
+      </c>
+      <c r="I16" s="24">
+        <v>-25</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="25">
+        <v>1</v>
+      </c>
+      <c r="R16" s="25">
+        <f>H16</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="24">
+        <v>1100</v>
+      </c>
+      <c r="H17" s="24">
+        <v>30</v>
+      </c>
+      <c r="I17" s="24">
+        <v>1070</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G18" s="24">
+        <v>760</v>
+      </c>
+      <c r="H18" s="24">
+        <v>30</v>
+      </c>
+      <c r="I18" s="24">
+        <v>730</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F19" s="28">
+        <v>1</v>
+      </c>
+      <c r="G19" s="24">
+        <v>875</v>
+      </c>
+      <c r="H19" s="24">
+        <v>25</v>
+      </c>
+      <c r="I19" s="24">
+        <v>850</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F20" s="28">
+        <v>1</v>
+      </c>
+      <c r="G20" s="24">
+        <v>375</v>
+      </c>
+      <c r="H20" s="24">
+        <v>25</v>
+      </c>
+      <c r="I20" s="24">
+        <v>350</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F21" s="28">
+        <v>1</v>
+      </c>
+      <c r="G21" s="24">
+        <v>405</v>
+      </c>
+      <c r="H21" s="24">
+        <v>25</v>
+      </c>
+      <c r="I21" s="24">
+        <v>380</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F22" s="28">
+        <v>1</v>
+      </c>
+      <c r="G22" s="24">
+        <v>885</v>
+      </c>
+      <c r="H22" s="24">
+        <v>25</v>
+      </c>
+      <c r="I22" s="24">
+        <v>860</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F23" s="28">
+        <v>4</v>
+      </c>
+      <c r="G23" s="24">
+        <v>405</v>
+      </c>
+      <c r="H23" s="24">
+        <v>25</v>
+      </c>
+      <c r="I23" s="24">
+        <v>380</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>2104</v>
+      </c>
+      <c r="F24" s="28">
+        <v>5</v>
+      </c>
+      <c r="G24" s="24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24">
+        <v>25</v>
+      </c>
+      <c r="I24" s="24">
+        <v>-25</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="25">
+        <v>1</v>
+      </c>
+      <c r="R24" s="25">
+        <f>H24</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F25" s="28">
+        <v>10</v>
+      </c>
+      <c r="G25" s="24">
+        <v>405</v>
+      </c>
+      <c r="H25" s="24">
+        <v>25</v>
+      </c>
+      <c r="I25" s="24">
+        <v>380</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="24">
+        <v>0</v>
+      </c>
+      <c r="H26" s="24">
+        <v>25</v>
+      </c>
+      <c r="I26" s="24">
+        <v>-25</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>2048</v>
+      </c>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="25">
+        <v>1</v>
+      </c>
+      <c r="R26" s="25">
+        <f>H26</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <f>SUBTOTAL(9,G3:G27)</f>
+        <v>9385</v>
+      </c>
+      <c r="H28">
+        <f>SUBTOTAL(9,H3:H27)</f>
+        <v>655</v>
+      </c>
+      <c r="I28">
+        <f>SUBTOTAL(9,I3:I27)</f>
+        <v>8730</v>
+      </c>
+      <c r="J28">
+        <f>SUBTOTAL(9,J3:J27)</f>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f>SUBTOTAL(9,K3:K27)</f>
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f>SUBTOTAL(9,L3:L27)</f>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f>SUBTOTAL(9,M3:M27)</f>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f>SUBTOTAL(9,N3:N27)</f>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f>SUBTOTAL(9,O3:O27)</f>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f>SUBTOTAL(9,P3:P27)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f>SUBTOTAL(9,Q3:Q27)</f>
+        <v>24</v>
+      </c>
+      <c r="R28">
+        <f>SUBTOTAL(9,R3:R27)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I29" s="29">
+        <v>-1450</v>
+      </c>
+      <c r="J29" s="30" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="7" t="s">
+        <v>2044</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J32" s="9" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H31" s="10" t="s">
+    <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H33" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="I31" s="11">
-        <f>SUM(I25:I29)</f>
-        <v>12295</v>
-      </c>
-      <c r="J31" s="11">
-        <f>Q26</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="H32" s="12" t="s">
+      <c r="I33" s="11">
+        <f>SUM(I27:I31)</f>
+        <v>7280</v>
+      </c>
+      <c r="J33" s="11">
+        <f>Q28</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H34" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="I32" s="13">
-        <f>R25</f>
+      <c r="I34" s="13">
+        <f>R28</f>
+        <v>120</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H35" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I35" s="13">
+        <f>S28</f>
         <v>0</v>
       </c>
-      <c r="J32" s="14"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H33" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="I33" s="13">
-        <f>S25</f>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H36" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I36" s="13">
+        <f>T28</f>
         <v>0</v>
       </c>
-      <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H34" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="I34" s="13">
-        <f>T25</f>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H37" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I37" s="13">
+        <f>U28</f>
         <v>0</v>
       </c>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H35" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="I35" s="13">
-        <f>U25</f>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H38" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H39" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+    </row>
+    <row r="40" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+      <c r="H40" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I40" s="19">
+        <f>SUM(I33:I39)</f>
+        <v>7400</v>
+      </c>
+      <c r="J40" s="19">
+        <f>SUM(J33:J37)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="27">
+        <v>1450</v>
+      </c>
+      <c r="F42" s="27">
         <v>0</v>
       </c>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H36" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H37" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-    </row>
-    <row r="38" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="H38" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I38" s="19">
-        <f>SUM(I31:I37)</f>
-        <v>12295</v>
-      </c>
-      <c r="J38" s="19">
-        <f>SUM(J31:J35)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>1730</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="F41" s="2">
-        <v>750</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="G42" s="27">
+        <v>1450</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="31" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D44" s="32">
+        <v>7</v>
+      </c>
+      <c r="E44" s="33">
+        <v>1320</v>
+      </c>
+      <c r="F44" s="33">
         <v>0</v>
       </c>
-      <c r="H41" s="2">
-        <f t="shared" ref="H41" si="2">F41-G41</f>
-        <v>750</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>1896</v>
+      <c r="G44" s="33">
+        <v>1320</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>2054</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>2048</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>2115</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P24" xr:uid="{74F114B3-91C2-4A35-9139-792FE289E983}"/>
+  <autoFilter ref="A2:P26" xr:uid="{95DC3523-A7E3-4CC1-8375-C845D3F25091}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25135,8 +28746,8 @@
         <v>319</v>
       </c>
       <c r="J55" s="13">
-        <f>S48</f>
-        <v>0</v>
+        <f>S49</f>
+        <v>260</v>
       </c>
       <c r="K55" s="14"/>
     </row>
@@ -25190,7 +28801,7 @@
       </c>
       <c r="J61" s="19">
         <f>SUM(J54:J60)</f>
-        <v>29560</v>
+        <v>29820</v>
       </c>
       <c r="K61" s="19">
         <f>SUM(K54:K58)</f>
@@ -27557,8 +31168,8 @@
         <v>319</v>
       </c>
       <c r="J55" s="13">
-        <f>S48</f>
-        <v>0</v>
+        <f>S49</f>
+        <v>335</v>
       </c>
       <c r="K55" s="14"/>
     </row>
@@ -27612,7 +31223,7 @@
       </c>
       <c r="J61" s="19">
         <f>SUM(J54:J60)</f>
-        <v>26705</v>
+        <v>27040</v>
       </c>
       <c r="K61" s="19">
         <f>SUM(K54:K58)</f>
@@ -29357,8 +32968,8 @@
         <v>319</v>
       </c>
       <c r="J42" s="13">
-        <f>S35</f>
-        <v>0</v>
+        <f>S36</f>
+        <v>145</v>
       </c>
       <c r="K42" s="14"/>
     </row>
@@ -29412,7 +33023,7 @@
       </c>
       <c r="J48" s="19">
         <f>SUM(J41:J47)</f>
-        <v>8077</v>
+        <v>8222</v>
       </c>
       <c r="K48" s="19">
         <f>SUM(K41:K45)</f>
@@ -32398,8 +36009,8 @@
         <v>319</v>
       </c>
       <c r="J67" s="13">
-        <f>S60</f>
-        <v>0</v>
+        <f>S61</f>
+        <v>310</v>
       </c>
       <c r="K67" s="14"/>
     </row>
@@ -32453,7 +36064,7 @@
       </c>
       <c r="J73" s="19">
         <f>SUM(J66:J72)</f>
-        <v>40115</v>
+        <v>40425</v>
       </c>
       <c r="K73" s="19">
         <f>SUM(K66:K70)</f>
@@ -35501,8 +39112,8 @@
         <v>319</v>
       </c>
       <c r="J68" s="13">
-        <f>S61</f>
-        <v>0</v>
+        <f>S62</f>
+        <v>485</v>
       </c>
       <c r="K68" s="14"/>
     </row>
@@ -35556,7 +39167,7 @@
       </c>
       <c r="J74" s="19">
         <f>SUM(J67:J73)</f>
-        <v>30138</v>
+        <v>30623</v>
       </c>
       <c r="K74" s="19">
         <f>SUM(K67:K71)</f>
@@ -38844,8 +42455,8 @@
         <v>319</v>
       </c>
       <c r="J73" s="13">
-        <f>S66</f>
-        <v>0</v>
+        <f>S67</f>
+        <v>420</v>
       </c>
       <c r="K73" s="14"/>
     </row>
@@ -38899,7 +42510,7 @@
       </c>
       <c r="J79" s="19">
         <f>SUM(J72:J78)</f>
-        <v>32630</v>
+        <v>33050</v>
       </c>
       <c r="K79" s="19">
         <f>SUM(K72:K76)</f>
@@ -40749,8 +44360,8 @@
         <v>319</v>
       </c>
       <c r="J45" s="13">
-        <f>S38</f>
-        <v>0</v>
+        <f>S39</f>
+        <v>250</v>
       </c>
       <c r="K45" s="14"/>
     </row>
@@ -40804,7 +44415,7 @@
       </c>
       <c r="J51" s="19">
         <f>SUM(J44:J50)</f>
-        <v>19745</v>
+        <v>19995</v>
       </c>
       <c r="K51" s="19">
         <f>SUM(K44:K48)</f>
@@ -42070,8 +45681,8 @@
         <v>319</v>
       </c>
       <c r="J32" s="13">
-        <f>S25</f>
-        <v>0</v>
+        <f>S26</f>
+        <v>75</v>
       </c>
       <c r="K32" s="14"/>
     </row>
@@ -42125,7 +45736,7 @@
       </c>
       <c r="J38" s="19">
         <f>SUM(J31:J37)</f>
-        <v>18185</v>
+        <v>18260</v>
       </c>
       <c r="K38" s="19">
         <f>SUM(K31:K35)</f>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A39F124-B57A-4BAF-A501-5F19BF2E5EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C394BEC9-5214-47A1-8F36-F2F45D37C947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="16" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-28920" yWindow="-150" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -6571,7 +6571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6623,8 +6623,7 @@
     <xf numFmtId="3" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -25295,7 +25294,9 @@
       <c r="Q5" s="25">
         <v>1</v>
       </c>
-      <c r="R5" s="25"/>
+      <c r="R5" s="25">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
@@ -26221,59 +26222,59 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G28">
-        <f>SUBTOTAL(9,G3:G27)</f>
+        <f t="shared" ref="G28:R28" si="0">SUBTOTAL(9,G3:G27)</f>
         <v>9385</v>
       </c>
       <c r="H28">
-        <f>SUBTOTAL(9,H3:H27)</f>
+        <f t="shared" si="0"/>
         <v>655</v>
       </c>
       <c r="I28">
-        <f>SUBTOTAL(9,I3:I27)</f>
+        <f t="shared" si="0"/>
         <v>8730</v>
       </c>
       <c r="J28">
-        <f>SUBTOTAL(9,J3:J27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28">
-        <f>SUBTOTAL(9,K3:K27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L28">
-        <f>SUBTOTAL(9,L3:L27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M28">
-        <f>SUBTOTAL(9,M3:M27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N28">
-        <f>SUBTOTAL(9,N3:N27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O28">
-        <f>SUBTOTAL(9,O3:O27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P28">
-        <f>SUBTOTAL(9,P3:P27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q28">
-        <f>SUBTOTAL(9,Q3:Q27)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="R28">
-        <f>SUBTOTAL(9,R3:R27)</f>
-        <v>120</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="I29" s="29">
         <v>-1450</v>
       </c>
-      <c r="J29" s="30" t="s">
+      <c r="J29" s="22" t="s">
         <v>329</v>
       </c>
     </row>
@@ -26307,7 +26308,7 @@
       </c>
       <c r="I34" s="13">
         <f>R28</f>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="J34" s="14"/>
     </row>
@@ -26361,7 +26362,7 @@
       </c>
       <c r="I40" s="19">
         <f>SUM(I33:I39)</f>
-        <v>7400</v>
+        <v>7430</v>
       </c>
       <c r="J40" s="19">
         <f>SUM(J33:J37)</f>
@@ -26414,34 +26415,34 @@
       </c>
     </row>
     <row r="44" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="30" t="s">
         <v>2051</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="30" t="s">
         <v>2052</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="30" t="s">
         <v>2053</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="31">
         <v>7</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="32">
         <v>1320</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="32">
         <v>0</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="32">
         <v>1320</v>
       </c>
-      <c r="H44" s="31" t="s">
+      <c r="H44" s="30" t="s">
         <v>2054</v>
       </c>
-      <c r="I44" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="31" t="s">
+      <c r="I44" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="30" t="s">
         <v>2048</v>
       </c>
       <c r="K44" s="3" t="s">

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C394BEC9-5214-47A1-8F36-F2F45D37C947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37379EA-0D71-413D-8A1A-F561BDBEA51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-150" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="16" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -6404,9 +6404,6 @@
     <t>165/1 bạch đằng p2</t>
   </si>
   <si>
-    <t>kh ck 1450</t>
-  </si>
-  <si>
     <t>NGAY 20-3</t>
   </si>
   <si>
@@ -6416,7 +6413,10 @@
     <t>NGAY 18-3</t>
   </si>
   <si>
-    <t>kh ck 1320</t>
+    <t>kh ck shop 1320</t>
+  </si>
+  <si>
+    <t>kh ck shop 1450</t>
   </si>
 </sst>
 </file>
@@ -22275,7 +22275,7 @@
         <v>489</v>
       </c>
       <c r="C1" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23381,7 +23381,7 @@
         <v>639</v>
       </c>
       <c r="C1" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25101,9 +25101,9 @@
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5703125" customWidth="1"/>
     <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -25111,7 +25111,7 @@
         <v>736</v>
       </c>
       <c r="C1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -25286,7 +25286,7 @@
         <v>2048</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="N5" s="21"/>
       <c r="O5" s="21"/>
@@ -26406,7 +26406,7 @@
         <v>1955</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -26446,7 +26446,7 @@
         <v>2048</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
   </sheetData>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37379EA-0D71-413D-8A1A-F561BDBEA51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899C7A69-00B2-4724-BA3F-8D525D668241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="16" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="17" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="18-3" sheetId="15" r:id="rId15"/>
     <sheet name="19-3" sheetId="16" r:id="rId16"/>
     <sheet name="20-3" sheetId="17" r:id="rId17"/>
+    <sheet name="21-3" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'10-3'!$A$2:$Q$37</definedName>
@@ -42,6 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'18-3'!$A$2:$P$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'19-3'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'20-3'!$A$2:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'21-3'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2-3'!$A$2:$Q$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4-3'!$A$2:$Q$47</definedName>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6543" uniqueCount="2116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6827" uniqueCount="2209">
   <si>
     <t>THU 2</t>
   </si>
@@ -6417,6 +6419,285 @@
   </si>
   <si>
     <t>kh ck shop 1450</t>
+  </si>
+  <si>
+    <t>kh ck shop 820</t>
+  </si>
+  <si>
+    <t>Nhung Dang</t>
+  </si>
+  <si>
+    <t>HD003482</t>
+  </si>
+  <si>
+    <t>17 Hưng gia3 Tân phong</t>
+  </si>
+  <si>
+    <t>AT 21-03</t>
+  </si>
+  <si>
+    <t>21-03-2026</t>
+  </si>
+  <si>
+    <t>Rose Love</t>
+  </si>
+  <si>
+    <t>HD003506</t>
+  </si>
+  <si>
+    <t>206 quách đình bảo phú thạnh</t>
+  </si>
+  <si>
+    <t>Le Bao Ngoc</t>
+  </si>
+  <si>
+    <t>HD003683</t>
+  </si>
+  <si>
+    <t>chung cư Century Celadon, phường Sơn Kỳ - Sảnh C5 cổng 1</t>
+  </si>
+  <si>
+    <t>Mr Adam/Fanee</t>
+  </si>
+  <si>
+    <t>HD003422</t>
+  </si>
+  <si>
+    <t>Chung cư Conic Reverside (Block A), Đường số 1, KDC Conic, khu phố 6</t>
+  </si>
+  <si>
+    <t>Bích Ngà</t>
+  </si>
+  <si>
+    <t>HD003643</t>
+  </si>
+  <si>
+    <t>Nhà 18 lỗ H đường số 2 khu dân cư phú mỹ cửa màu đen có 2 cây mai to đường hoàng quốc việt quẹo vào, phường phú mỹ</t>
+  </si>
+  <si>
+    <t>Nhi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD003289</t>
+  </si>
+  <si>
+    <t>1185 lê đức anh khu phố 5 phường an lạc</t>
+  </si>
+  <si>
+    <t>Dung Nguyễn</t>
+  </si>
+  <si>
+    <t>HD003503</t>
+  </si>
+  <si>
+    <t>1123 quốc lộ 1ạ, tân tạo, chung cư an gia the star</t>
+  </si>
+  <si>
+    <t>Trịnh Hoài Thương</t>
+  </si>
+  <si>
+    <t>HD003358</t>
+  </si>
+  <si>
+    <t>75 tô hiệu phú thạnh</t>
+  </si>
+  <si>
+    <t>LDVKH</t>
+  </si>
+  <si>
+    <t>HD003456</t>
+  </si>
+  <si>
+    <t>177c, Đường Số 1, P. Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Mercy Nguyễn Phu</t>
+  </si>
+  <si>
+    <t>HD003706</t>
+  </si>
+  <si>
+    <t>298/16/8B Tân Hoà Đông P bình trị đông</t>
+  </si>
+  <si>
+    <t>HD003593</t>
+  </si>
+  <si>
+    <t>Dream Home Palace (1436 Trịnh Quang Nghị, P7)</t>
+  </si>
+  <si>
+    <t>g nghi</t>
+  </si>
+  <si>
+    <t>Ngọc Dung</t>
+  </si>
+  <si>
+    <t>HD003412</t>
+  </si>
+  <si>
+    <t>2581/79a huỳnh tấn phát</t>
+  </si>
+  <si>
+    <t>Từ Thụy Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>HD003555</t>
+  </si>
+  <si>
+    <t>154/136/15/3 Au luong lan p3</t>
+  </si>
+  <si>
+    <t>Cherry Nguyên</t>
+  </si>
+  <si>
+    <t>HD003731</t>
+  </si>
+  <si>
+    <t>A4/40A2 Tổ 4 ấp 1A đường 1C, xã Vĩnh Lộc B</t>
+  </si>
+  <si>
+    <t>HD003685</t>
+  </si>
+  <si>
+    <t>Thanh Thao</t>
+  </si>
+  <si>
+    <t>HD003554</t>
+  </si>
+  <si>
+    <t>1053/23/5 lê đức thọ p16</t>
+  </si>
+  <si>
+    <t>Trần Mỹ Nhi</t>
+  </si>
+  <si>
+    <t>HD003684</t>
+  </si>
+  <si>
+    <t>352 Nguyễn xí p13</t>
+  </si>
+  <si>
+    <t>Phạm Dung</t>
+  </si>
+  <si>
+    <t>HD003689</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh phường 22 chung cư vinhome - toà lanmark 5</t>
+  </si>
+  <si>
+    <t>Quyên Nguyễn</t>
+  </si>
+  <si>
+    <t>HD003233</t>
+  </si>
+  <si>
+    <t>The opera residence tháp B scala</t>
+  </si>
+  <si>
+    <t>Chị Nhậm ( gửi đồ cho Julie em chị Hà ở Úc) - fb Gia Khánh Linh</t>
+  </si>
+  <si>
+    <t>HD003539</t>
+  </si>
+  <si>
+    <t>40/8 xuân Thuỷ - Thảo Điền</t>
+  </si>
+  <si>
+    <t>Kim Phú</t>
+  </si>
+  <si>
+    <t>HD003644</t>
+  </si>
+  <si>
+    <t>89/57 đường số 59 p14</t>
+  </si>
+  <si>
+    <t>Tâm Như</t>
+  </si>
+  <si>
+    <t>HD003500</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, phường 3, Phường Gò Vấp</t>
+  </si>
+  <si>
+    <t>Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD003498</t>
+  </si>
+  <si>
+    <t>79a đường số 12 linh tây</t>
+  </si>
+  <si>
+    <t>Tên Khải fb : Lysa Kim</t>
+  </si>
+  <si>
+    <t>HD003566</t>
+  </si>
+  <si>
+    <t>124 Nam kỳ khởi nghĩa, phường bến nghé</t>
+  </si>
+  <si>
+    <t>cô hai fb MeiLing Loke</t>
+  </si>
+  <si>
+    <t>HD003670</t>
+  </si>
+  <si>
+    <t>52/20 hồ thị kỷ f1 gặp cô 2</t>
+  </si>
+  <si>
+    <t>giàu - gửi hàng cho Mỹ Phùng</t>
+  </si>
+  <si>
+    <t>HD003541</t>
+  </si>
+  <si>
+    <t>37 Đặng Minh Trứ, Phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Hoàng Yến Như</t>
+  </si>
+  <si>
+    <t>HD003699</t>
+  </si>
+  <si>
+    <t>145/11 Nguyễn Văn Trỗi, phường Phú Nhuận</t>
+  </si>
+  <si>
+    <t>Thuý Ngân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD003531</t>
+  </si>
+  <si>
+    <t>257/6/11A Phan xích Long p 2</t>
+  </si>
+  <si>
+    <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD003567</t>
+  </si>
+  <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
+    <t>nhà xe Khải Nam</t>
+  </si>
+  <si>
+    <t>363 Đường Hùng vương P. 9</t>
+  </si>
+  <si>
+    <t>Thanh Hằng ( Vivi Kosalim )</t>
+  </si>
+  <si>
+    <t>605 Âu Cơ, Phường Phú Trung</t>
+  </si>
+  <si>
+    <t>NGAY 21-3</t>
   </si>
 </sst>
 </file>
@@ -6488,7 +6769,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6543,8 +6824,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6567,11 +6854,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6627,6 +6927,14 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25095,6 +25403,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="87.85546875" bestFit="1" customWidth="1"/>
@@ -26451,6 +26760,1729 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:P26" xr:uid="{95DC3523-A7E3-4CC1-8375-C845D3F25091}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3C7F64-476C-4050-A86D-BF329FE968BC}">
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F3" s="23">
+        <v>7</v>
+      </c>
+      <c r="G3" s="23">
+        <v>890</v>
+      </c>
+      <c r="H3" s="23">
+        <v>30</v>
+      </c>
+      <c r="I3" s="23">
+        <f>G3-H3</f>
+        <v>860</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1325</v>
+      </c>
+      <c r="H4" s="23">
+        <v>25</v>
+      </c>
+      <c r="I4" s="23">
+        <f>G4-H4</f>
+        <v>1300</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G5" s="23">
+        <v>765</v>
+      </c>
+      <c r="H5" s="23">
+        <v>25</v>
+      </c>
+      <c r="I5" s="23">
+        <f>G5-H5</f>
+        <v>740</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F6" s="23">
+        <v>8</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23">
+        <v>25</v>
+      </c>
+      <c r="I6" s="23">
+        <f>-H6</f>
+        <v>-25</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="23">
+        <v>1</v>
+      </c>
+      <c r="R6" s="25">
+        <f>H6</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F7" s="23">
+        <v>7</v>
+      </c>
+      <c r="G7" s="23">
+        <v>670</v>
+      </c>
+      <c r="H7" s="23">
+        <v>30</v>
+      </c>
+      <c r="I7" s="23">
+        <f>G7-H7</f>
+        <v>640</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G8" s="23">
+        <v>890</v>
+      </c>
+      <c r="H8" s="23">
+        <v>30</v>
+      </c>
+      <c r="I8" s="23">
+        <f>G8-H8</f>
+        <v>860</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G9" s="23">
+        <v>2010</v>
+      </c>
+      <c r="H9" s="23">
+        <v>30</v>
+      </c>
+      <c r="I9" s="23">
+        <f>G9-H9</f>
+        <v>1980</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G10" s="23">
+        <v>405</v>
+      </c>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f>G10-H10</f>
+        <v>380</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>2145</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23">
+        <v>25</v>
+      </c>
+      <c r="I11" s="23">
+        <f>-H11</f>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="23">
+        <v>1</v>
+      </c>
+      <c r="R11" s="25">
+        <f>H11</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G12" s="23">
+        <v>610</v>
+      </c>
+      <c r="H12" s="23">
+        <v>30</v>
+      </c>
+      <c r="I12" s="23">
+        <f>G12-H12</f>
+        <v>580</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G13" s="23">
+        <v>380</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f>G13-H13</f>
+        <v>350</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G14" s="23">
+        <v>625</v>
+      </c>
+      <c r="H14" s="23">
+        <v>35</v>
+      </c>
+      <c r="I14" s="23">
+        <f>G14-H14</f>
+        <v>590</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F15" s="23">
+        <v>8</v>
+      </c>
+      <c r="G15" s="23">
+        <v>405</v>
+      </c>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f>G15-H15</f>
+        <v>380</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>2159</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="G16" s="23">
+        <v>995</v>
+      </c>
+      <c r="H16" s="23">
+        <v>35</v>
+      </c>
+      <c r="I16" s="23">
+        <f>G16-H16</f>
+        <v>960</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="36" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F17" s="37">
+        <v>7</v>
+      </c>
+      <c r="G17" s="37">
+        <v>0</v>
+      </c>
+      <c r="H17" s="37">
+        <v>30</v>
+      </c>
+      <c r="I17" s="37">
+        <f>-H17</f>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>2120</v>
+      </c>
+      <c r="K17" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="36" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M17" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="37">
+        <v>1</v>
+      </c>
+      <c r="R17" s="34">
+        <f>H17</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="23">
+        <v>975</v>
+      </c>
+      <c r="H18" s="23">
+        <v>25</v>
+      </c>
+      <c r="I18" s="23">
+        <f>G18-H18</f>
+        <v>950</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>2167</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="23">
+        <v>600</v>
+      </c>
+      <c r="H19" s="23">
+        <v>20</v>
+      </c>
+      <c r="I19" s="23">
+        <f>G19-H19</f>
+        <v>580</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="23">
+        <v>660</v>
+      </c>
+      <c r="H20" s="23">
+        <v>20</v>
+      </c>
+      <c r="I20" s="23">
+        <f>G20-H20</f>
+        <v>640</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F21" s="23">
+        <v>2</v>
+      </c>
+      <c r="G21" s="23">
+        <v>750</v>
+      </c>
+      <c r="H21" s="23">
+        <v>30</v>
+      </c>
+      <c r="I21" s="23">
+        <f>G21-H21</f>
+        <v>720</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F22" s="23">
+        <v>2</v>
+      </c>
+      <c r="G22" s="23">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f>-H22</f>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="23">
+        <v>1</v>
+      </c>
+      <c r="R22" s="25">
+        <f>H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="23">
+        <v>745</v>
+      </c>
+      <c r="H23" s="23">
+        <v>25</v>
+      </c>
+      <c r="I23" s="23">
+        <f>G23-H23</f>
+        <v>720</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="23">
+        <v>755</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f>G24-H24</f>
+        <v>730</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="23">
+        <v>520</v>
+      </c>
+      <c r="H25" s="23">
+        <v>30</v>
+      </c>
+      <c r="I25" s="23">
+        <f>G25-H25</f>
+        <v>490</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23">
+        <v>365</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f>G26-H26</f>
+        <v>340</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F27" s="23">
+        <v>10</v>
+      </c>
+      <c r="G27" s="23">
+        <v>785</v>
+      </c>
+      <c r="H27" s="23">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <f>G27-H27</f>
+        <v>760</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f>-H28</f>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="23">
+        <v>1</v>
+      </c>
+      <c r="R28" s="25">
+        <f t="shared" ref="R28:R29" si="0">H28</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>20</v>
+      </c>
+      <c r="I29" s="23">
+        <f>-H29</f>
+        <v>-20</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="23">
+        <v>1</v>
+      </c>
+      <c r="R29" s="25">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="23">
+        <v>610</v>
+      </c>
+      <c r="H30" s="23">
+        <v>20</v>
+      </c>
+      <c r="I30" s="23">
+        <f>G30-H30</f>
+        <v>590</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>25</v>
+      </c>
+      <c r="I31" s="23">
+        <f>-H31</f>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="23">
+        <v>1</v>
+      </c>
+      <c r="R31" s="25">
+        <f t="shared" ref="R31:R32" si="1">H31</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F32" s="23">
+        <v>5</v>
+      </c>
+      <c r="G32" s="23">
+        <v>0</v>
+      </c>
+      <c r="H32" s="23">
+        <v>30</v>
+      </c>
+      <c r="I32" s="23">
+        <f>-H32</f>
+        <v>-30</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="23">
+        <v>1</v>
+      </c>
+      <c r="R32" s="25">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>2035</v>
+      </c>
+      <c r="F33" s="23">
+        <v>4</v>
+      </c>
+      <c r="G33" s="23">
+        <v>30</v>
+      </c>
+      <c r="H33" s="23">
+        <v>30</v>
+      </c>
+      <c r="I33" s="23">
+        <f>G33-H33</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G34" s="23">
+        <v>40</v>
+      </c>
+      <c r="H34" s="23">
+        <v>40</v>
+      </c>
+      <c r="I34" s="23">
+        <f>G34-H34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>1888</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <f>SUBTOTAL(9,G3:G35)</f>
+        <v>16805</v>
+      </c>
+      <c r="H36">
+        <f t="shared" ref="H36:R36" si="2">SUBTOTAL(9,H3:H35)</f>
+        <v>875</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>15930</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I37" s="29">
+        <v>-820</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I38" s="29"/>
+      <c r="J38" s="22"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I39" s="29"/>
+      <c r="J39" s="22"/>
+    </row>
+    <row r="40" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="H40" s="7" t="s">
+        <v>2044</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H41" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="I41" s="38">
+        <f>SUM(I35:I39)</f>
+        <v>15110</v>
+      </c>
+      <c r="J41" s="11">
+        <f>Q36</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I42" s="13">
+        <f>R36</f>
+        <v>210</v>
+      </c>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I43" s="13">
+        <f>S28</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H44" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="I44" s="13">
+        <f>T28</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H45" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="I45" s="13">
+        <f>U28</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H46" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H47" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="H48" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I48" s="19">
+        <f>SUM(I41:I47)</f>
+        <v>15320</v>
+      </c>
+      <c r="J48" s="19">
+        <f>SUM(J41:J45)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D50" s="27">
+        <v>12</v>
+      </c>
+      <c r="E50" s="27">
+        <v>820</v>
+      </c>
+      <c r="F50" s="27">
+        <v>0</v>
+      </c>
+      <c r="G50" s="27">
+        <v>820</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{95DC3523-A7E3-4CC1-8375-C845D3F25091}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F949A4F5-1D2B-4D0B-BA1A-F802C936D4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201D6C93-A636-49C1-8662-9B053CA08085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="24" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -9145,7 +9145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -9222,6 +9222,7 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24970,7 +24971,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="4">
+      <c r="Q3" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25015,7 +25016,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4">
+      <c r="Q4" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25058,7 +25059,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="Q5">
+      <c r="Q5" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25101,7 +25102,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-      <c r="Q6">
+      <c r="Q6" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25144,7 +25145,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
       <c r="P7" s="21"/>
-      <c r="Q7" s="22">
+      <c r="Q7" s="42">
         <v>1</v>
       </c>
       <c r="R7" s="22">
@@ -25193,7 +25194,7 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
-      <c r="Q8">
+      <c r="Q8" s="50">
         <v>1</v>
       </c>
       <c r="R8" s="22">
@@ -25240,7 +25241,7 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
-      <c r="Q9">
+      <c r="Q9" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25285,7 +25286,7 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
-      <c r="Q10">
+      <c r="Q10" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25328,7 +25329,7 @@
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
-      <c r="Q11">
+      <c r="Q11" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25371,7 +25372,7 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
-      <c r="Q12">
+      <c r="Q12" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25414,7 +25415,7 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
-      <c r="Q13">
+      <c r="Q13" s="50">
         <v>1</v>
       </c>
       <c r="R13" s="22">
@@ -25461,7 +25462,7 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
-      <c r="Q14">
+      <c r="Q14" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25504,7 +25505,7 @@
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
-      <c r="Q15">
+      <c r="Q15" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25547,7 +25548,7 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-      <c r="Q16">
+      <c r="Q16" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25590,7 +25591,7 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
-      <c r="Q17">
+      <c r="Q17" s="50">
         <v>1</v>
       </c>
       <c r="R17" s="22">
@@ -25637,7 +25638,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-      <c r="Q18">
+      <c r="Q18" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25680,7 +25681,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
-      <c r="Q19">
+      <c r="Q19" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25723,7 +25724,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-      <c r="Q20">
+      <c r="Q20" s="50">
         <v>1</v>
       </c>
     </row>
@@ -25766,7 +25767,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-      <c r="Q21">
+      <c r="Q21" s="50">
         <v>1</v>
       </c>
     </row>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201D6C93-A636-49C1-8662-9B053CA08085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB21CA52-0C5B-40EE-A7C4-0BAEDE8D98F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="25" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="27-3" sheetId="23" r:id="rId23"/>
     <sheet name="28-3" sheetId="24" r:id="rId24"/>
     <sheet name="30-3" sheetId="25" r:id="rId25"/>
+    <sheet name="31-3" sheetId="26" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'10-3'!$A$2:$Q$37</definedName>
@@ -59,6 +60,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'27-3'!$A$2:$P$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'28-3'!$A$2:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'30-3'!$A$2:$P$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'31-3'!$A$2:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'3-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'4-3'!$A$2:$Q$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5-3'!$A$2:$Q$34</definedName>
@@ -85,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9036" uniqueCount="2960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9279" uniqueCount="3030">
   <si>
     <t>THU 2</t>
   </si>
@@ -8965,6 +8967,216 @@
   </si>
   <si>
     <t>số 217Đường bùi thị xuân phường 1</t>
+  </si>
+  <si>
+    <t>NGAY 31-3</t>
+  </si>
+  <si>
+    <t>Quỳnh Hương</t>
+  </si>
+  <si>
+    <t>HD006634</t>
+  </si>
+  <si>
+    <t>Saigon Royal Residences Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
+    <t>Trần Huyền</t>
+  </si>
+  <si>
+    <t>HD006209</t>
+  </si>
+  <si>
+    <t>Số 27, Đường D5, Phường Tân Thuận Tây</t>
+  </si>
+  <si>
+    <t>AT 31-03</t>
+  </si>
+  <si>
+    <t>MC Sanita Mao (MVO1908)</t>
+  </si>
+  <si>
+    <t>HD006501</t>
+  </si>
+  <si>
+    <t>Khoai Tây</t>
+  </si>
+  <si>
+    <t>HD006429</t>
+  </si>
+  <si>
+    <t>chung cư tera mia đường số 2 kdc B intressco, xã bình hưng</t>
+  </si>
+  <si>
+    <t>HD006492</t>
+  </si>
+  <si>
+    <t>HD006490</t>
+  </si>
+  <si>
+    <t>Minh Vy</t>
+  </si>
+  <si>
+    <t>HD006528</t>
+  </si>
+  <si>
+    <t>688/23/1c hương lộ 2 bình trị đông A</t>
+  </si>
+  <si>
+    <t>Cái Tiệm Lút ( Hong Nhu My )</t>
+  </si>
+  <si>
+    <t>HD006529</t>
+  </si>
+  <si>
+    <t>107 Trương Minh Ký, P13</t>
+  </si>
+  <si>
+    <t>Khánh Như</t>
+  </si>
+  <si>
+    <t>HD006441</t>
+  </si>
+  <si>
+    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Winnie Chua</t>
+  </si>
+  <si>
+    <t>HD006544</t>
+  </si>
+  <si>
+    <t>210 bùi văn ba p.tan thuận đông kdc Jamona golden silk đường N3 căn M8</t>
+  </si>
+  <si>
+    <t>Nguyễn Lý Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD006531</t>
+  </si>
+  <si>
+    <t>137/31/14 phan anh phường bình trị đông</t>
+  </si>
+  <si>
+    <t>Đông Nhi</t>
+  </si>
+  <si>
+    <t>HD006448</t>
+  </si>
+  <si>
+    <t>93 đường số 1, phường 4(phường 1 hoặc phường Hạnh Thông)</t>
+  </si>
+  <si>
+    <t>HD006228</t>
+  </si>
+  <si>
+    <t>29/18 đường số 5 bình trưng đông</t>
+  </si>
+  <si>
+    <t>X.Anh</t>
+  </si>
+  <si>
+    <t>HD006503</t>
+  </si>
+  <si>
+    <t>Căn 603, lô B2 chung cư orchard parkview, 130-132 hồng hà, p. Đức nhuận</t>
+  </si>
+  <si>
+    <t>Thanh Ngân</t>
+  </si>
+  <si>
+    <t>HD006607</t>
+  </si>
+  <si>
+    <t>37 trương vĩnh ký, phường Tân Thạnh</t>
+  </si>
+  <si>
+    <t>HD006389</t>
+  </si>
+  <si>
+    <t>Chung cư lavida plus Nguyễn Văn Linh, phường Tân Phong</t>
+  </si>
+  <si>
+    <t>Hanh Corado</t>
+  </si>
+  <si>
+    <t>HD006621</t>
+  </si>
+  <si>
+    <t>09 Đường số 2, P. An Khánh</t>
+  </si>
+  <si>
+    <t>Vân NA Vy</t>
+  </si>
+  <si>
+    <t>HD006405</t>
+  </si>
+  <si>
+    <t>251 đường 9a khu trung sơn, bình hưng</t>
+  </si>
+  <si>
+    <t>HD006546</t>
+  </si>
+  <si>
+    <t>Trang Lê</t>
+  </si>
+  <si>
+    <t>HD006288</t>
+  </si>
+  <si>
+    <t>8A Sông Thương P2</t>
+  </si>
+  <si>
+    <t>CU519450/pepanhaketya</t>
+  </si>
+  <si>
+    <t>HD006539</t>
+  </si>
+  <si>
+    <t>HD006452</t>
+  </si>
+  <si>
+    <t>431/7b đường Phan Văn Trị phường 7</t>
+  </si>
+  <si>
+    <t>Thanh Thúy</t>
+  </si>
+  <si>
+    <t>HD006512</t>
+  </si>
+  <si>
+    <t>346 quang trung, phường thông tây hội</t>
+  </si>
+  <si>
+    <t>W2459</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp 21, Tổ 3, Kp3</t>
+  </si>
+  <si>
+    <t>BN882</t>
+  </si>
+  <si>
+    <t>Ivy Huyền</t>
+  </si>
+  <si>
+    <t>Số 5 Nhất Chi Mai phường 13</t>
+  </si>
+  <si>
+    <t>dolly dolly</t>
+  </si>
+  <si>
+    <t>HD006339</t>
+  </si>
+  <si>
+    <t>21 võ trường toản thảo điền</t>
+  </si>
+  <si>
+    <t>đơn trả 31.3</t>
   </si>
 </sst>
 </file>
@@ -9145,7 +9357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -9223,6 +9435,7 @@
     <xf numFmtId="3" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -45093,14 +45306,14 @@
         <v>98</v>
       </c>
       <c r="G35" s="25">
-        <v>2110</v>
+        <v>2080</v>
       </c>
       <c r="H35" s="25">
         <v>30</v>
       </c>
       <c r="I35" s="25">
         <f>G35-H35</f>
-        <v>2080</v>
+        <v>2050</v>
       </c>
       <c r="J35" t="s">
         <v>25</v>
@@ -45111,8 +45324,15 @@
       <c r="L35" t="s">
         <v>2788</v>
       </c>
+      <c r="M35" s="51" t="s">
+        <v>2403</v>
+      </c>
       <c r="Q35" s="25">
         <v>1</v>
+      </c>
+      <c r="R35" s="25">
+        <f>H35</f>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -46435,7 +46655,7 @@
     <row r="70" spans="2:18" x14ac:dyDescent="0.25">
       <c r="G70">
         <f t="shared" ref="G70:R70" si="5">SUBTOTAL(9,G3:G69)</f>
-        <v>36560</v>
+        <v>36530</v>
       </c>
       <c r="H70">
         <f t="shared" si="5"/>
@@ -46443,7 +46663,7 @@
       </c>
       <c r="I70">
         <f t="shared" si="5"/>
-        <v>34755</v>
+        <v>34725</v>
       </c>
       <c r="J70">
         <f t="shared" si="5"/>
@@ -46479,7 +46699,7 @@
       </c>
       <c r="R70">
         <f t="shared" si="5"/>
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.25">
@@ -46511,7 +46731,7 @@
       </c>
       <c r="I75" s="38">
         <f>SUM(I69:I73)</f>
-        <v>34755</v>
+        <v>34725</v>
       </c>
       <c r="J75" s="11">
         <f>Q70</f>
@@ -46524,7 +46744,7 @@
       </c>
       <c r="I76" s="13">
         <f>R70</f>
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="J76" s="14"/>
     </row>
@@ -46589,6 +46809,1387 @@
   <autoFilter ref="A2:P68" xr:uid="{00000000-0009-0000-0000-000012000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P68">
       <sortCondition ref="J2:J68"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBECAA7D-DAFD-43D3-91E7-B48D33E77E74}">
+  <dimension ref="A1:R44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2967</v>
+      </c>
+      <c r="F3" s="25">
+        <v>7</v>
+      </c>
+      <c r="G3" s="25">
+        <v>700</v>
+      </c>
+      <c r="H3" s="25">
+        <v>30</v>
+      </c>
+      <c r="I3" s="25">
+        <f>G3-H3</f>
+        <v>670</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2969</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2970</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G4" s="25">
+        <v>0</v>
+      </c>
+      <c r="H4" s="25">
+        <v>30</v>
+      </c>
+      <c r="I4" s="25">
+        <f>G4-H4</f>
+        <v>-30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q4" s="25">
+        <v>1</v>
+      </c>
+      <c r="R4" s="25">
+        <f>H4</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G5" s="25">
+        <v>415</v>
+      </c>
+      <c r="H5" s="25">
+        <v>35</v>
+      </c>
+      <c r="I5" s="25">
+        <f>G5-H5</f>
+        <v>380</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2978</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G6" s="25">
+        <v>0</v>
+      </c>
+      <c r="H6" s="25">
+        <v>30</v>
+      </c>
+      <c r="I6" s="25">
+        <f>G6-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>1</v>
+      </c>
+      <c r="R6" s="25">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2983</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2984</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G7" s="25">
+        <v>740</v>
+      </c>
+      <c r="H7" s="25">
+        <v>30</v>
+      </c>
+      <c r="I7" s="25">
+        <f>G7-H7</f>
+        <v>710</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2987</v>
+      </c>
+      <c r="F8" s="25">
+        <v>7</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0</v>
+      </c>
+      <c r="H8" s="25">
+        <v>30</v>
+      </c>
+      <c r="I8" s="25">
+        <f>G8-H8</f>
+        <v>-30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>1</v>
+      </c>
+      <c r="R8" s="25">
+        <f>H8</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G9" s="25">
+        <v>1030</v>
+      </c>
+      <c r="H9" s="25">
+        <v>30</v>
+      </c>
+      <c r="I9" s="25">
+        <f>G9-H9</f>
+        <v>1000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3001</v>
+      </c>
+      <c r="F10" t="s">
+        <v>607</v>
+      </c>
+      <c r="G10" s="25">
+        <v>915</v>
+      </c>
+      <c r="H10" s="25">
+        <v>25</v>
+      </c>
+      <c r="I10" s="25">
+        <f>G10-H10</f>
+        <v>890</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3002</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F11" s="25">
+        <v>7</v>
+      </c>
+      <c r="G11" s="25">
+        <v>800</v>
+      </c>
+      <c r="H11" s="25">
+        <v>30</v>
+      </c>
+      <c r="I11" s="25">
+        <f>G11-H11</f>
+        <v>770</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3007</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3009</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G12" s="25">
+        <v>745</v>
+      </c>
+      <c r="H12" s="25">
+        <v>35</v>
+      </c>
+      <c r="I12" s="25">
+        <f>G12-H12</f>
+        <v>710</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2947</v>
+      </c>
+      <c r="F13" s="25">
+        <v>8</v>
+      </c>
+      <c r="G13" s="25">
+        <v>30</v>
+      </c>
+      <c r="H13" s="25">
+        <v>30</v>
+      </c>
+      <c r="I13" s="25">
+        <f>G13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M13" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F14" s="25">
+        <v>6</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0</v>
+      </c>
+      <c r="H14" s="25">
+        <v>30</v>
+      </c>
+      <c r="I14" s="25">
+        <f>G14-H14</f>
+        <v>-30</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>1</v>
+      </c>
+      <c r="R14" s="25">
+        <f t="shared" ref="R14:R16" si="0">H14</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2980</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="25">
+        <v>0</v>
+      </c>
+      <c r="H15" s="25">
+        <v>25</v>
+      </c>
+      <c r="I15" s="25">
+        <f>G15-H15</f>
+        <v>-25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>1</v>
+      </c>
+      <c r="R15" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2991</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2992</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2993</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="25">
+        <v>0</v>
+      </c>
+      <c r="H16" s="25">
+        <v>25</v>
+      </c>
+      <c r="I16" s="25">
+        <f>G16-H16</f>
+        <v>-25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>1</v>
+      </c>
+      <c r="R16" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2921</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2995</v>
+      </c>
+      <c r="F17" s="25">
+        <v>2</v>
+      </c>
+      <c r="G17" s="25">
+        <v>700</v>
+      </c>
+      <c r="H17" s="25">
+        <v>30</v>
+      </c>
+      <c r="I17" s="25">
+        <f>G17-H17</f>
+        <v>670</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3004</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3005</v>
+      </c>
+      <c r="E18" t="s">
+        <v>3006</v>
+      </c>
+      <c r="F18" s="25">
+        <v>2</v>
+      </c>
+      <c r="G18" s="25">
+        <v>820</v>
+      </c>
+      <c r="H18" s="25">
+        <v>30</v>
+      </c>
+      <c r="I18" s="25">
+        <f>G18-H18</f>
+        <v>790</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E19" t="s">
+        <v>3020</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="25">
+        <v>945</v>
+      </c>
+      <c r="H19" s="25">
+        <v>25</v>
+      </c>
+      <c r="I19" s="25">
+        <f>G19-H19</f>
+        <v>920</v>
+      </c>
+      <c r="J19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E20" t="s">
+        <v>3022</v>
+      </c>
+      <c r="F20" s="25">
+        <v>12</v>
+      </c>
+      <c r="G20" s="25">
+        <v>0</v>
+      </c>
+      <c r="H20" s="25">
+        <v>35</v>
+      </c>
+      <c r="I20" s="25">
+        <f>G20-H20</f>
+        <v>-35</v>
+      </c>
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>1</v>
+      </c>
+      <c r="R20" s="25">
+        <f t="shared" ref="R20:R21" si="1">H20</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F21" s="25">
+        <v>12</v>
+      </c>
+      <c r="G21" s="25">
+        <v>0</v>
+      </c>
+      <c r="H21" s="25">
+        <v>35</v>
+      </c>
+      <c r="I21" s="25">
+        <f>G21-H21</f>
+        <v>-35</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>1</v>
+      </c>
+      <c r="R21" s="25">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3024</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3025</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="25">
+        <v>30</v>
+      </c>
+      <c r="H22" s="25">
+        <v>30</v>
+      </c>
+      <c r="I22" s="25">
+        <f>G22-H22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D23" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E23" t="s">
+        <v>3028</v>
+      </c>
+      <c r="F23" s="25">
+        <v>2</v>
+      </c>
+      <c r="G23" s="25">
+        <v>2945</v>
+      </c>
+      <c r="H23" s="25">
+        <v>35</v>
+      </c>
+      <c r="I23" s="25">
+        <f>G23-H23</f>
+        <v>2910</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2962</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2963</v>
+      </c>
+      <c r="F24" s="25">
+        <v>4</v>
+      </c>
+      <c r="G24" s="25">
+        <v>815</v>
+      </c>
+      <c r="H24" s="25">
+        <v>25</v>
+      </c>
+      <c r="I24" s="25">
+        <f>G24-H24</f>
+        <v>790</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F25" s="25">
+        <v>10</v>
+      </c>
+      <c r="G25" s="25">
+        <v>885</v>
+      </c>
+      <c r="H25" s="25">
+        <v>25</v>
+      </c>
+      <c r="I25" s="25">
+        <f>G25-H25</f>
+        <v>860</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q25" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2975</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F26" s="25">
+        <v>1</v>
+      </c>
+      <c r="G26" s="25">
+        <v>815</v>
+      </c>
+      <c r="H26" s="25">
+        <v>25</v>
+      </c>
+      <c r="I26" s="25">
+        <f>G26-H26</f>
+        <v>790</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K26" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q26" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="25">
+        <v>810</v>
+      </c>
+      <c r="H27" s="25">
+        <v>20</v>
+      </c>
+      <c r="I27" s="25">
+        <f>G27-H27</f>
+        <v>790</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3013</v>
+      </c>
+      <c r="F28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="25">
+        <v>845</v>
+      </c>
+      <c r="H28" s="25">
+        <v>25</v>
+      </c>
+      <c r="I28" s="25">
+        <f>G28-H28</f>
+        <v>820</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q28" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D29" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2860</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="25">
+        <v>0</v>
+      </c>
+      <c r="H29" s="25">
+        <v>25</v>
+      </c>
+      <c r="I29" s="25">
+        <f>G29-H29</f>
+        <v>-25</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Q29" s="25">
+        <v>1</v>
+      </c>
+      <c r="R29" s="25">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D30" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3017</v>
+      </c>
+      <c r="F30" s="25">
+        <v>5</v>
+      </c>
+      <c r="G30" s="25">
+        <v>55</v>
+      </c>
+      <c r="H30" s="25">
+        <v>25</v>
+      </c>
+      <c r="I30" s="25">
+        <f>G30-H30</f>
+        <v>30</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M30" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q30" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <f>SUBTOTAL(9,G3:G31)</f>
+        <v>15040</v>
+      </c>
+      <c r="H32">
+        <f>SUBTOTAL(9,H3:H31)</f>
+        <v>805</v>
+      </c>
+      <c r="I32">
+        <f>SUBTOTAL(9,I3:I31)</f>
+        <v>14235</v>
+      </c>
+      <c r="J32">
+        <f>SUBTOTAL(9,J3:J31)</f>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f>SUBTOTAL(9,K3:K31)</f>
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <f>SUBTOTAL(9,L3:L31)</f>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f>SUBTOTAL(9,M3:M31)</f>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f>SUBTOTAL(9,N3:N31)</f>
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <f>SUBTOTAL(9,O3:O31)</f>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f>SUBTOTAL(9,P3:P31)</f>
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <f>SUBTOTAL(9,Q3:Q31)</f>
+        <v>28</v>
+      </c>
+      <c r="R32">
+        <f>SUBTOTAL(9,R3:R31)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I33" s="29">
+        <v>-2630</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I34" s="29"/>
+      <c r="J34" s="22"/>
+    </row>
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I35" s="29"/>
+      <c r="J35" s="22"/>
+    </row>
+    <row r="36" spans="8:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="7" t="s">
+        <v>2787</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="37" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I37" s="38">
+        <f>SUM(I31:I35)</f>
+        <v>11605</v>
+      </c>
+      <c r="J37" s="11">
+        <f>Q32</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="I38" s="13">
+        <f>R32</f>
+        <v>265</v>
+      </c>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H39" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="I39" s="13">
+        <f>S32</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H40" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="I40" s="13">
+        <f>T32</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H41" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I41" s="13">
+        <f>U32</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+    </row>
+    <row r="43" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+    </row>
+    <row r="44" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H44" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="I44" s="39">
+        <f>SUM(I37:I43)</f>
+        <v>11870</v>
+      </c>
+      <c r="J44" s="19">
+        <f>SUM(J37:J41)</f>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P30" xr:uid="{00000000-0009-0000-0000-000012000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P30">
+      <sortCondition ref="J2:J30"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB21CA52-0C5B-40EE-A7C4-0BAEDE8D98F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F46BE4-0E34-4645-A82F-83EEC2D62E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="25" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9279" uniqueCount="3030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9289" uniqueCount="3031">
   <si>
     <t>THU 2</t>
   </si>
@@ -9176,14 +9176,17 @@
     <t>21 võ trường toản thảo điền</t>
   </si>
   <si>
-    <t>đơn trả 31.3</t>
+    <t>đơn trả 1.2</t>
+  </si>
+  <si>
+    <t>kh ck shop 745</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9252,6 +9255,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -9357,7 +9367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -9436,6 +9446,8 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -46818,7 +46830,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBECAA7D-DAFD-43D3-91E7-B48D33E77E74}">
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -46894,1192 +46906,1355 @@
         <v>18</v>
       </c>
       <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>2965</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>2966</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>2967</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="23">
         <v>7</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="23">
         <v>700</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="23">
         <v>30</v>
       </c>
-      <c r="I3" s="25">
-        <f>G3-H3</f>
+      <c r="I3" s="23">
+        <f t="shared" ref="I3:I30" si="0">G3-H3</f>
         <v>670</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q3" s="25">
-        <v>1</v>
-      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="23">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>2969</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>2970</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
         <v>2276</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>1853</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <v>0</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="23">
         <v>30</v>
       </c>
-      <c r="I4" s="25">
-        <f>G4-H4</f>
+      <c r="I4" s="23">
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q4" s="25">
-        <v>1</v>
-      </c>
-      <c r="R4" s="25">
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="23">
+        <v>1</v>
+      </c>
+      <c r="R4" s="23">
         <f>H4</f>
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>2971</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>2972</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>2973</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>1976</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="23">
         <v>415</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="23">
         <v>35</v>
       </c>
-      <c r="I5" s="25">
-        <f>G5-H5</f>
+      <c r="I5" s="23">
+        <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q5" s="25">
-        <v>1</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="23">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>2976</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>2977</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>2978</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="5" t="s">
         <v>1853</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="23">
         <v>0</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="23">
         <v>30</v>
       </c>
-      <c r="I6" s="25">
-        <f>G6-H6</f>
+      <c r="I6" s="23">
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="K6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q6" s="25">
-        <v>1</v>
-      </c>
-      <c r="R6" s="25">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="23">
+        <v>1</v>
+      </c>
+      <c r="R6" s="23">
         <f>H6</f>
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>2982</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>2983</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
         <v>2984</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="5" t="s">
         <v>1853</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="23">
         <v>740</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="23">
         <v>30</v>
       </c>
-      <c r="I7" s="25">
-        <f>G7-H7</f>
+      <c r="I7" s="23">
+        <f t="shared" si="0"/>
         <v>710</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="K7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q7" s="25">
-        <v>1</v>
-      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="23">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>2985</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>2986</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="5" t="s">
         <v>2987</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="23">
         <v>7</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="23">
         <v>0</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="23">
         <v>30</v>
       </c>
-      <c r="I8" s="25">
-        <f>G8-H8</f>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q8" s="25">
-        <v>1</v>
-      </c>
-      <c r="R8" s="25">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="23">
+        <v>1</v>
+      </c>
+      <c r="R8" s="23">
         <f>H8</f>
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>2988</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>2989</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="5" t="s">
         <v>2990</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="5" t="s">
         <v>1853</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="23">
         <v>1030</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="23">
         <v>30</v>
       </c>
-      <c r="I9" s="25">
-        <f>G9-H9</f>
+      <c r="I9" s="23">
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="K9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q9" s="25">
-        <v>1</v>
-      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="23">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>2999</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>3000</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5" t="s">
         <v>3001</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="23">
         <v>915</v>
       </c>
-      <c r="H10" s="25">
-        <v>25</v>
-      </c>
-      <c r="I10" s="25">
-        <f>G10-H10</f>
+      <c r="H10" s="23">
+        <v>25</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q10" s="25">
-        <v>1</v>
-      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="23">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>2797</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>3002</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="5" t="s">
         <v>3003</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="23">
         <v>7</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="23">
         <v>800</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="23">
         <v>30</v>
       </c>
-      <c r="I11" s="25">
-        <f>G11-H11</f>
+      <c r="I11" s="23">
+        <f t="shared" si="0"/>
         <v>770</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="K11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q11" s="25">
-        <v>1</v>
-      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="23">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>3007</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>3008</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="5" t="s">
         <v>3009</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="5" t="s">
         <v>1976</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="23">
         <v>745</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="23">
         <v>35</v>
       </c>
-      <c r="I12" s="25">
-        <f>G12-H12</f>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
         <v>710</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="K12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q12" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="23">
+        <v>1</v>
+      </c>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36" t="s">
         <v>1827</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="36" t="s">
         <v>2945</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="36" t="s">
         <v>3010</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="36" t="s">
         <v>2947</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="37">
         <v>8</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="37">
         <v>30</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="37">
         <v>30</v>
       </c>
-      <c r="I13" s="25">
-        <f>G13-H13</f>
+      <c r="I13" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="36" t="s">
         <v>2968</v>
       </c>
-      <c r="K13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="K13" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="36" t="s">
         <v>2964</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="Q13" s="25">
-        <v>1</v>
-      </c>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="37">
+        <v>1</v>
+      </c>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="5" t="s">
         <v>1833</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>2292</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
         <v>1841</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="23">
         <v>6</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="23">
         <v>0</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="23">
         <v>30</v>
       </c>
-      <c r="I14" s="25">
-        <f>G14-H14</f>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="5" t="s">
         <v>2968</v>
       </c>
-      <c r="K14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="K14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q14" s="25">
-        <v>1</v>
-      </c>
-      <c r="R14" s="25">
-        <f t="shared" ref="R14:R16" si="0">H14</f>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="23">
+        <v>1</v>
+      </c>
+      <c r="R14" s="23">
+        <f t="shared" ref="R14:R16" si="1">H14</f>
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>2979</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
         <v>2980</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="5" t="s">
         <v>2981</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="23">
         <v>0</v>
       </c>
-      <c r="H15" s="25">
-        <v>25</v>
-      </c>
-      <c r="I15" s="25">
-        <f>G15-H15</f>
+      <c r="H15" s="23">
+        <v>25</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="J15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="J15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q15" s="25">
-        <v>1</v>
-      </c>
-      <c r="R15" s="25">
-        <f t="shared" si="0"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="23">
+        <v>1</v>
+      </c>
+      <c r="R15" s="23">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>2991</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>2992</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="5" t="s">
         <v>2993</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="23">
         <v>0</v>
       </c>
-      <c r="H16" s="25">
-        <v>25</v>
-      </c>
-      <c r="I16" s="25">
-        <f>G16-H16</f>
+      <c r="H16" s="23">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
-      <c r="J16" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="J16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q16" s="25">
-        <v>1</v>
-      </c>
-      <c r="R16" s="25">
-        <f t="shared" si="0"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="23">
+        <v>1</v>
+      </c>
+      <c r="R16" s="23">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>2921</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
         <v>2994</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="5" t="s">
         <v>2995</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="23">
         <v>2</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="23">
         <v>700</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="23">
         <v>30</v>
       </c>
-      <c r="I17" s="25">
-        <f>G17-H17</f>
+      <c r="I17" s="23">
+        <f t="shared" si="0"/>
         <v>670</v>
       </c>
-      <c r="J17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="J17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q17" s="25">
-        <v>1</v>
-      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="23">
+        <v>1</v>
+      </c>
+      <c r="R17" s="5"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>3004</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>3005</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="5" t="s">
         <v>3006</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="23">
         <v>2</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="23">
         <v>820</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="23">
         <v>30</v>
       </c>
-      <c r="I18" s="25">
-        <f>G18-H18</f>
+      <c r="I18" s="23">
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="J18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="J18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q18" s="25">
-        <v>1</v>
-      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="23">
+        <v>1</v>
+      </c>
+      <c r="R18" s="5"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>3018</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
         <v>3019</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="5" t="s">
         <v>3020</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="23">
         <v>945</v>
       </c>
-      <c r="H19" s="25">
-        <v>25</v>
-      </c>
-      <c r="I19" s="25">
-        <f>G19-H19</f>
+      <c r="H19" s="23">
+        <v>25</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="J19" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="J19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q19" s="25">
-        <v>1</v>
-      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="23">
+        <v>1</v>
+      </c>
+      <c r="R19" s="5"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>1833</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>3021</v>
       </c>
-      <c r="E20" t="s">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
         <v>3022</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="23">
         <v>12</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="23">
         <v>0</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="23">
         <v>35</v>
       </c>
-      <c r="I20" s="25">
-        <f>G20-H20</f>
+      <c r="I20" s="23">
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
-      <c r="J20" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="J20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q20" s="25">
-        <v>1</v>
-      </c>
-      <c r="R20" s="25">
-        <f t="shared" ref="R20:R21" si="1">H20</f>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="23">
+        <v>1</v>
+      </c>
+      <c r="R20" s="23">
+        <f t="shared" ref="R20:R21" si="2">H20</f>
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>1833</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>3023</v>
       </c>
-      <c r="E21" t="s">
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="s">
         <v>1892</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="23">
         <v>12</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="23">
         <v>0</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="23">
+        <v>45</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="0"/>
+        <v>-45</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="23">
+        <v>1</v>
+      </c>
+      <c r="R21" s="23">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>3025</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="23">
+        <v>30</v>
+      </c>
+      <c r="H22" s="23">
+        <v>30</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="23">
+        <v>1</v>
+      </c>
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>3028</v>
+      </c>
+      <c r="F23" s="23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="23">
+        <v>2910</v>
+      </c>
+      <c r="H23" s="23">
         <v>35</v>
       </c>
-      <c r="I21" s="25">
-        <f>G21-H21</f>
-        <v>-35</v>
-      </c>
-      <c r="J21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="I23" s="23">
+        <f t="shared" si="0"/>
+        <v>2875</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>2964</v>
       </c>
-      <c r="Q21" s="25">
-        <v>1</v>
-      </c>
-      <c r="R21" s="25">
-        <f t="shared" si="1"/>
+      <c r="M23" s="6" t="s">
+        <v>2403</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="23">
+        <v>1</v>
+      </c>
+      <c r="R23" s="23">
+        <f>H23</f>
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1833</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="C22" t="s">
-        <v>3024</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3025</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="C24" s="5" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>2962</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>2963</v>
+      </c>
+      <c r="F24" s="23">
+        <v>4</v>
+      </c>
+      <c r="G24" s="23">
+        <v>815</v>
+      </c>
+      <c r="H24" s="23">
+        <v>25</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="23">
+        <v>1</v>
+      </c>
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F25" s="23">
+        <v>10</v>
+      </c>
+      <c r="G25" s="23">
+        <v>885</v>
+      </c>
+      <c r="H25" s="23">
+        <v>25</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="23">
+        <v>1</v>
+      </c>
+      <c r="R25" s="5"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1</v>
+      </c>
+      <c r="G26" s="23">
+        <v>815</v>
+      </c>
+      <c r="H26" s="23">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="23">
+        <v>1</v>
+      </c>
+      <c r="R26" s="5"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="23">
+        <v>810</v>
+      </c>
+      <c r="H27" s="23">
+        <v>20</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="23">
+        <v>1</v>
+      </c>
+      <c r="R27" s="5"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G28" s="23">
+        <v>845</v>
+      </c>
+      <c r="H28" s="23">
+        <v>25</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="23">
+        <v>1</v>
+      </c>
+      <c r="R28" s="5"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="23">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="23">
+        <v>1</v>
+      </c>
+      <c r="R29" s="23">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36"/>
+      <c r="B30" s="36" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>3017</v>
+      </c>
+      <c r="F30" s="37">
+        <v>5</v>
+      </c>
+      <c r="G30" s="37">
+        <v>55</v>
+      </c>
+      <c r="H30" s="37">
+        <v>25</v>
+      </c>
+      <c r="I30" s="37">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H22" s="25">
-        <v>30</v>
-      </c>
-      <c r="I22" s="25">
-        <f>G22-H22</f>
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="J30" s="36" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K30" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="36" t="s">
         <v>2964</v>
       </c>
-      <c r="Q22" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3026</v>
-      </c>
-      <c r="D23" t="s">
-        <v>3027</v>
-      </c>
-      <c r="E23" t="s">
-        <v>3028</v>
-      </c>
-      <c r="F23" s="25">
-        <v>2</v>
-      </c>
-      <c r="G23" s="25">
-        <v>2945</v>
-      </c>
-      <c r="H23" s="25">
-        <v>35</v>
-      </c>
-      <c r="I23" s="25">
-        <f>G23-H23</f>
-        <v>2910</v>
-      </c>
-      <c r="J23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q23" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C24" t="s">
-        <v>2961</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2962</v>
-      </c>
-      <c r="E24" t="s">
-        <v>2963</v>
-      </c>
-      <c r="F24" s="25">
-        <v>4</v>
-      </c>
-      <c r="G24" s="25">
-        <v>815</v>
-      </c>
-      <c r="H24" s="25">
-        <v>25</v>
-      </c>
-      <c r="I24" s="25">
-        <f>G24-H24</f>
-        <v>790</v>
-      </c>
-      <c r="J24" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K24" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q24" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1937</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2974</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F25" s="25">
-        <v>10</v>
-      </c>
-      <c r="G25" s="25">
-        <v>885</v>
-      </c>
-      <c r="H25" s="25">
-        <v>25</v>
-      </c>
-      <c r="I25" s="25">
-        <f>G25-H25</f>
-        <v>860</v>
-      </c>
-      <c r="J25" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K25" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q25" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C26" t="s">
-        <v>2017</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2975</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2019</v>
-      </c>
-      <c r="F26" s="25">
-        <v>1</v>
-      </c>
-      <c r="G26" s="25">
-        <v>815</v>
-      </c>
-      <c r="H26" s="25">
-        <v>25</v>
-      </c>
-      <c r="I26" s="25">
-        <f>G26-H26</f>
-        <v>790</v>
-      </c>
-      <c r="J26" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K26" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q26" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2996</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2997</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2998</v>
-      </c>
-      <c r="F27" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="25">
-        <v>810</v>
-      </c>
-      <c r="H27" s="25">
-        <v>20</v>
-      </c>
-      <c r="I27" s="25">
-        <f>G27-H27</f>
-        <v>790</v>
-      </c>
-      <c r="J27" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K27" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q27" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C28" t="s">
-        <v>3011</v>
-      </c>
-      <c r="D28" t="s">
-        <v>3012</v>
-      </c>
-      <c r="E28" t="s">
-        <v>3013</v>
-      </c>
-      <c r="F28" t="s">
-        <v>98</v>
-      </c>
-      <c r="G28" s="25">
-        <v>845</v>
-      </c>
-      <c r="H28" s="25">
-        <v>25</v>
-      </c>
-      <c r="I28" s="25">
-        <f>G28-H28</f>
-        <v>820</v>
-      </c>
-      <c r="J28" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K28" t="s">
-        <v>25</v>
-      </c>
-      <c r="L28" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q28" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3014</v>
-      </c>
-      <c r="D29" t="s">
-        <v>3015</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2860</v>
-      </c>
-      <c r="F29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G29" s="25">
-        <v>0</v>
-      </c>
-      <c r="H29" s="25">
-        <v>25</v>
-      </c>
-      <c r="I29" s="25">
-        <f>G29-H29</f>
-        <v>-25</v>
-      </c>
-      <c r="J29" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K29" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" t="s">
-        <v>2964</v>
-      </c>
-      <c r="Q29" s="25">
-        <v>1</v>
-      </c>
-      <c r="R29" s="25">
-        <f>H29</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2824</v>
-      </c>
-      <c r="D30" t="s">
-        <v>3016</v>
-      </c>
-      <c r="E30" t="s">
-        <v>3017</v>
-      </c>
-      <c r="F30" s="25">
-        <v>5</v>
-      </c>
-      <c r="G30" s="25">
-        <v>55</v>
-      </c>
-      <c r="H30" s="25">
-        <v>25</v>
-      </c>
-      <c r="I30" s="25">
-        <f>G30-H30</f>
-        <v>30</v>
-      </c>
-      <c r="J30" t="s">
-        <v>1884</v>
-      </c>
-      <c r="K30" t="s">
-        <v>25</v>
-      </c>
-      <c r="L30" t="s">
-        <v>2964</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="M30" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="Q30" s="25">
-        <v>1</v>
-      </c>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="37">
+        <v>1</v>
+      </c>
+      <c r="R30" s="36"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G32">
-        <f>SUBTOTAL(9,G3:G31)</f>
-        <v>15040</v>
+        <f t="shared" ref="G32:R32" si="3">SUBTOTAL(9,G3:G31)</f>
+        <v>15005</v>
       </c>
       <c r="H32">
-        <f>SUBTOTAL(9,H3:H31)</f>
-        <v>805</v>
+        <f t="shared" si="3"/>
+        <v>815</v>
       </c>
       <c r="I32">
-        <f>SUBTOTAL(9,I3:I31)</f>
-        <v>14235</v>
+        <f t="shared" si="3"/>
+        <v>14190</v>
       </c>
       <c r="J32">
-        <f>SUBTOTAL(9,J3:J31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K32">
-        <f>SUBTOTAL(9,K3:K31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L32">
-        <f>SUBTOTAL(9,L3:L31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M32">
-        <f>SUBTOTAL(9,M3:M31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32">
-        <f>SUBTOTAL(9,N3:N31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O32">
-        <f>SUBTOTAL(9,O3:O31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P32">
-        <f>SUBTOTAL(9,P3:P31)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q32">
-        <f>SUBTOTAL(9,Q3:Q31)</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="R32">
-        <f>SUBTOTAL(9,R3:R31)</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I33" s="29">
         <v>-2630</v>
       </c>
@@ -48087,15 +48262,19 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="I34" s="29"/>
-      <c r="J34" s="22"/>
-    </row>
-    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I34" s="29">
+        <v>-745</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I35" s="29"/>
       <c r="J35" s="22"/>
     </row>
-    <row r="36" spans="8:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H36" s="7" t="s">
         <v>2787</v>
       </c>
@@ -48106,30 +48285,30 @@
         <v>314</v>
       </c>
     </row>
-    <row r="37" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H37" s="10" t="s">
         <v>315</v>
       </c>
       <c r="I37" s="38">
         <f>SUM(I31:I35)</f>
-        <v>11605</v>
+        <v>10815</v>
       </c>
       <c r="J37" s="11">
         <f>Q32</f>
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H38" s="12" t="s">
         <v>316</v>
       </c>
       <c r="I38" s="13">
         <f>R32</f>
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="J38" s="14"/>
     </row>
-    <row r="39" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H39" s="12" t="s">
         <v>317</v>
       </c>
@@ -48139,7 +48318,7 @@
       </c>
       <c r="J39" s="14"/>
     </row>
-    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H40" s="12" t="s">
         <v>318</v>
       </c>
@@ -48149,7 +48328,7 @@
       </c>
       <c r="J40" s="14"/>
     </row>
-    <row r="41" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H41" s="12" t="s">
         <v>319</v>
       </c>
@@ -48159,31 +48338,72 @@
       </c>
       <c r="J41" s="14"/>
     </row>
-    <row r="42" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H42" s="15" t="s">
         <v>320</v>
       </c>
       <c r="I42" s="16"/>
       <c r="J42" s="16"/>
     </row>
-    <row r="43" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H43" s="17" t="s">
         <v>321</v>
       </c>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
     </row>
-    <row r="44" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H44" s="18" t="s">
         <v>322</v>
       </c>
       <c r="I44" s="39">
         <f>SUM(I37:I43)</f>
-        <v>11870</v>
+        <v>11125</v>
       </c>
       <c r="J44" s="19">
         <f>SUM(J37:J41)</f>
         <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="52" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B48" s="52" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D48" s="53">
+        <v>4</v>
+      </c>
+      <c r="E48" s="53">
+        <v>745</v>
+      </c>
+      <c r="F48" s="53">
+        <v>0</v>
+      </c>
+      <c r="G48" s="53">
+        <f t="shared" ref="G48" si="4">E48-F48</f>
+        <v>745</v>
+      </c>
+      <c r="H48" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="52" t="s">
+        <v>2788</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>3030</v>
       </c>
     </row>
   </sheetData>

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F46BE4-0E34-4645-A82F-83EEC2D62E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967116A2-038C-4333-A5E6-7CBD1C67E161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="25" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{5C19E60F-B0EA-4466-8994-298A0AC29210}"/>
   </bookViews>
   <sheets>
     <sheet name="2-3" sheetId="1" r:id="rId1"/>
@@ -26202,6 +26202,7 @@
     <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">

--- a/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Mar/THÁNG 3.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
